--- a/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa joue dans le salon. Maman est sur le canapé. Léa a des cubes. Les cubes sont verts et jaunes. Léa fait une tour. La tour est haute. Les cubes font clic. Puis le jeu est fini. Maman dit : c'est l'heure de ranger. Léa prend un cube. Elle le met dans la caisse. Elle prend un autre cube. Elle le met dans la caisse. Encore un cube. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Maman dit : merci Léa.</t>
+          <t>Léa joue dans le salon. Maman est sur le canapé. Léa a des cubes. Les cubes sont verts et jaunes. Léa fait une tour. La tour est haute. Les cubes font clic. Puis le jeu est fini. C'est l'heure de ranger. Léa prend un cube. Elle le met dans la caisse. Elle prend un autre cube. Elle le met dans la caisse. Encore un cube. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Merci Léa.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,14 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa joue dans le salon. Maman est sur le canapé. Léa a des cubes. Les cubes sont verts et jaunes. Léa fait une tour. La tour est haute. Les cubes font clic. Puis le jeu est fini.
+maman|C'est l'heure de ranger.
+narrateur|Léa prend un cube. Elle le met dans la caisse. Elle prend un autre cube. Elle le met dans la caisse. Encore un cube. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse.
+maman|Merci Léa.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1489,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Après le jeu, que fait Léa ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1662,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a rangé. Les cubes sont dans la caisse. Le tapis est libre. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1829,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Léa ferme la caisse. Ça fait toc. Maman lui tend l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1996,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2036,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1313,6 +1318,7 @@
 maman|Merci Léa.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1502,7 @@
           <t>narrateur|Après le jeu, que fait Léa ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1667,6 +1674,7 @@
           <t>narrateur|Léa a rangé. Les cubes sont dans la caisse. Le tapis est libre. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1834,6 +1842,7 @@
           <t>narrateur|Léa ferme la caisse. Ça fait toc. Maman lui tend l'eau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2001,6 +2010,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2019,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2043,6 +2053,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2057,7 +2081,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2244,6 +2268,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Léa range les cubes</t>
+          <t>La bande de soleil et les cubes</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un cube jaune vit dans la bande de soleil. Après le jeu, Raphaël le met dans la caisse.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa joue dans le salon. Maman est sur le canapé. Léa a des cubes. Les cubes sont verts et jaunes. Léa fait une tour. La tour est haute. Les cubes font clic. Puis le jeu est fini. C'est l'heure de ranger. Léa prend un cube. Elle le met dans la caisse. Elle prend un autre cube. Elle le met dans la caisse. Encore un cube. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Merci Léa.</t>
+          <t>Le soleil entre par la fenêtre. Une bande jaune est sur le plancher. Un petit grain de poussière danse. La maison sent le pain chaud. Maman ouvre un tiroir. Ça fait un petit bruit. Le pain est bientôt prêt ! Merci, papa. Le tapis du salon est doux. Des cubes attendent près du canapé. Ils sont verts. Ils sont jaunes. En ce moment, Raphaël est au salon. Il touche un cube jaune. Le cube est lisse. Il est chaud, maman. C'est le soleil, Raphaël. Raphaël pose un cube. Puis un autre cube. Clic. La tour grandit. Elle est haute. Ta tour est belle ! Elle est haute, papa. Raphaël pose encore un cube. Clic. Puis le jeu est fini. Le jeu est fini, Raphaël. C'est l'heure de ranger. Ranger, c'est mettre dans la caisse. Raphaël regarde la caisse. La caisse est en bois. Elle sent le bois. Il prend un cube jaune. Il le met dans la caisse. Toc. Il prend un cube vert. Il le met dans la caisse. Toc. Bravo, Raphaël. Tu mets les cubes dans la caisse. Encore un cube. Dans la caisse. Papa arrive du couloir. Tu as fini de ranger tes jouets ? Presque, papa. Raphaël prend le dernier cube. Il le met dans la caisse. La caisse est pleine. Le tapis est vide. Le soleil est encore sur le plancher. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,10 +1324,59 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Léa joue dans le salon. Maman est sur le canapé. Léa a des cubes. Les cubes sont verts et jaunes. Léa fait une tour. La tour est haute. Les cubes font clic. Puis le jeu est fini.
+          <t>narrateur|Le soleil entre par la fenêtre.
+narrateur|Une bande jaune est sur le plancher.
+narrateur|Un petit grain de poussière danse.
+narrateur|La maison sent le pain chaud.
+narrateur|Maman ouvre un tiroir.
+narrateur|Ça fait un petit bruit.
+papa|Le pain est bientôt prêt !
+maman|Merci, papa.
+narrateur|Le tapis du salon est doux.
+narrateur|Des cubes attendent près du canapé.
+narrateur|Ils sont verts.
+narrateur|Ils sont jaunes.
+narrateur|En ce moment, Raphaël est au salon.
+narrateur|Il touche un cube jaune.
+narrateur|Le cube est lisse.
+enfant-m|Il est chaud, maman.
+maman|C'est le soleil, Raphaël.
+narrateur|Raphaël pose un cube.
+narrateur|Puis un autre cube.
+narrateur|Clic.
+narrateur|La tour grandit.
+narrateur|Elle est haute.
+papa|Ta tour est belle !
+enfant-m|Elle est haute, papa.
+narrateur|Raphaël pose encore un cube.
+narrateur|Clic.
+narrateur|Puis le jeu est fini.
+maman|Le jeu est fini, Raphaël.
 maman|C'est l'heure de ranger.
-narrateur|Léa prend un cube. Elle le met dans la caisse. Elle prend un autre cube. Elle le met dans la caisse. Encore un cube. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse.
-maman|Merci Léa.</t>
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Raphaël regarde la caisse.
+narrateur|La caisse est en bois.
+narrateur|Elle sent le bois.
+narrateur|Il prend un cube jaune.
+narrateur|Il le met dans la caisse.
+narrateur|Toc.
+narrateur|Il prend un cube vert.
+narrateur|Il le met dans la caisse.
+narrateur|Toc.
+maman|Bravo, Raphaël.
+maman|Tu mets les cubes dans la caisse.
+narrateur|Encore un cube.
+narrateur|Dans la caisse.
+narrateur|Papa arrive du couloir.
+papa|Tu as fini de ranger tes jouets ?
+enfant-m|Presque, papa.
+narrateur|Raphaël prend le dernier cube.
+narrateur|Il le met dans la caisse.
+narrateur|La caisse est pleine.
+narrateur|Le tapis est vide.
+narrateur|Le soleil est encore sur le plancher.
+maman|Merci, Raphaël.
+maman|Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1343,7 +1404,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Après le jeu, que fait Léa ?</t>
+          <t>Après le jeu, que fait Raphaël ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1499,7 +1560,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Après le jeu, que fait Léa ?</t>
+          <t>narrateur|Après le jeu, que fait Raphaël ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1527,7 +1588,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa a rangé. Les cubes sont dans la caisse. Le tapis est libre. Maman est là.</t>
+          <t>Raphaël a rangé. Les cubes sont dans la caisse. Le tapis est libre. Les pieds peuvent marcher. Le salon est calme, maintenant. Bravo. Les cubes sont rentrés dans la caisse. J'ai rangé. Oui. Ranger, c'est mettre dans la caisse. Raphaël pose la main sur le couvercle. Le bois est lisse. Tu as fini de ranger tes jouets ? Oui, papa. C'est du bon travail.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1671,7 +1732,21 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa a rangé. Les cubes sont dans la caisse. Le tapis est libre. Maman est là.</t>
+          <t>narrateur|Raphaël a rangé.
+narrateur|Les cubes sont dans la caisse.
+narrateur|Le tapis est libre.
+narrateur|Les pieds peuvent marcher.
+maman|Le salon est calme, maintenant.
+papa|Bravo.
+papa|Les cubes sont rentrés dans la caisse.
+enfant-m|J'ai rangé.
+maman|Oui.
+maman|Ranger, c'est mettre dans la caisse.
+narrateur|Raphaël pose la main sur le couvercle.
+narrateur|Le bois est lisse.
+papa|Tu as fini de ranger tes jouets ?
+enfant-m|Oui, papa.
+maman|C'est du bon travail.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1699,7 +1774,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Léa ferme la caisse. Ça fait toc. Maman lui tend l'eau.</t>
+          <t>Raphaël ferme la caisse. Ça fait toc. Le soleil touche le couvercle. Tu veux un peu d'eau ? Oui, maman. Maman lui tend un verre. L'eau fait un petit bruit. Raphaël boit une gorgée. Merci, Raphaël. Le salon est beau. Ils restent un moment. Le tapis est doux sous les pieds. On reste encore un peu ensemble ? Oui. Bravo.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1839,7 +1914,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Léa ferme la caisse. Ça fait toc. Maman lui tend l'eau.</t>
+          <t>narrateur|Raphaël ferme la caisse.
+narrateur|Ça fait toc.
+narrateur|Le soleil touche le couvercle.
+maman|Tu veux un peu d'eau ?
+enfant-m|Oui, maman.
+narrateur|Maman lui tend un verre.
+narrateur|L'eau fait un petit bruit.
+narrateur|Raphaël boit une gorgée.
+papa|Merci, Raphaël.
+papa|Le salon est beau.
+narrateur|Ils restent un moment.
+narrateur|Le tapis est doux sous les pieds.
+maman|On reste encore un peu ensemble ?
+enfant-m|Oui.
+maman|Bravo.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1867,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai mis les cubes dans la caisse. Bravo. Tu as fait du bon travail. La tour est rangée. Le soleil glisse un peu. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2007,7 +2096,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai mis les cubes dans la caisse.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+papa|La tour est rangée.
+narrateur|Le soleil glisse un peu.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2029,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2067,6 +2161,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La bande de soleil et les cubes</t>
+          <t>La nappe à carreaux</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Un cube jaune vit dans la bande de soleil. Après le jeu, Raphaël le met dans la caisse.</t>
+          <t>Raphaël veut le gâteau sur la nappe à carreaux. Un cube fait une bosse. Il met les cubes dans la caisse. Ils goûtent.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le soleil entre par la fenêtre. Une bande jaune est sur le plancher. Un petit grain de poussière danse. La maison sent le pain chaud. Maman ouvre un tiroir. Ça fait un petit bruit. Le pain est bientôt prêt ! Merci, papa. Le tapis du salon est doux. Des cubes attendent près du canapé. Ils sont verts. Ils sont jaunes. En ce moment, Raphaël est au salon. Il touche un cube jaune. Le cube est lisse. Il est chaud, maman. C'est le soleil, Raphaël. Raphaël pose un cube. Puis un autre cube. Clic. La tour grandit. Elle est haute. Ta tour est belle ! Elle est haute, papa. Raphaël pose encore un cube. Clic. Puis le jeu est fini. Le jeu est fini, Raphaël. C'est l'heure de ranger. Ranger, c'est mettre dans la caisse. Raphaël regarde la caisse. La caisse est en bois. Elle sent le bois. Il prend un cube jaune. Il le met dans la caisse. Toc. Il prend un cube vert. Il le met dans la caisse. Toc. Bravo, Raphaël. Tu mets les cubes dans la caisse. Encore un cube. Dans la caisse. Papa arrive du couloir. Tu as fini de ranger tes jouets ? Presque, papa. Raphaël prend le dernier cube. Il le met dans la caisse. La caisse est pleine. Le tapis est vide. Le soleil est encore sur le plancher. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>La cuillère en bois tape dans le bol. Ça sent la vanille. Une buée est sur la vitre de la cuisine. Une goutte glisse tout doucement. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend sur la chaise. Elle est encore pliée. Le tissu est doux. Et voilà Raphaël, près du tapis. Des cubes verts attendent. Des cubes jaunes aussi. Je fais une tour, maman. Pendant que le gâteau refroidit ? Oui. Une tour haute. Raphaël pose un cube vert. Clic. Puis un cube jaune. Clic. La tour grandit au milieu. Elle est belle, ta tour. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Raphaël pose encore un cube. Clic. Il touche le cube du haut. Le bois est lisse. On mange le vrai, après ? Oui. Sur la nappe. Maman prend la nappe à carreaux. Elle sent un peu le savon. Raphaël aide à l'ouvrir. La nappe se déplie sur le tapis. Un coin se replie. Raphaël l'aplatit avec la main. Il y a une bosse au milieu. Oh. Ça fait une bosse. Un cube est sous le tissu. La nappe ne peut pas être plate. Le gâteau a besoin d'une nappe plate. Je voulais le gâteau ici. Les cubes sont encore là. La tour attend près de la chaise. D'autres cubes sont sur le tapis. La bosse reste au milieu. Le plat va danser. Oui. Il faut de la place.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa joue dans le salon. Maman est sur le canapé. Léa a des cubes. Les cubes sont verts et jaunes. Léa fait une tour. La tour est haute. Les cubes font clic. Puis le jeu est fini. Maman dit : c'est l'heure de &lt;emphasis level="moderate"&gt;ranger&lt;/emphasis&gt;. Léa prend un cube. Elle le met dans la caisse. Elle prend un autre cube. Elle le met dans la caisse. Encore un cube. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Maman dit : merci Léa.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La cuillère en bois tape dans le bol. Ça sent la vanille. Une buée est sur la vitre de la cuisine. Une goutte glisse tout doucement. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend sur la chaise. Elle est encore pliée. Le tissu est doux. Et voilà Raphaël, près du tapis. Des cubes verts attendent. Des cubes jaunes aussi. Je fais une tour, maman. Pendant que le gâteau refroidit ? Oui. Une tour haute. Raphaël pose un cube vert. Clic. Puis un cube jaune. Clic. La tour grandit au milieu. Elle est belle, ta tour. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Raphaël pose encore un cube. Clic. Il touche le cube du haut. Le bois est lisse. On mange le vrai, après ? Oui. Sur la nappe. Maman prend la nappe à carreaux. Elle sent un peu le savon. Raphaël aide à l'ouvrir. La nappe se déplie sur le tapis. Un coin se replie. Raphaël l'aplatit avec la main. Il y a une bosse au milieu. Oh. Ça fait une bosse. Un cube est sous le tissu. La nappe ne peut pas être plate. Le gâteau a besoin d'une nappe plate. Je voulais le gâteau ici. Les cubes sont encore là. La tour attend près de la chaise. D'autres cubes sont sur le tapis. La bosse reste au milieu. Le plat va danser. Oui. Il faut de la place.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,62 +1324,56 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le soleil entre par la fenêtre.
-narrateur|Une bande jaune est sur le plancher.
-narrateur|Un petit grain de poussière danse.
-narrateur|La maison sent le pain chaud.
-narrateur|Maman ouvre un tiroir.
-narrateur|Ça fait un petit bruit.
-papa|Le pain est bientôt prêt !
-maman|Merci, papa.
-narrateur|Le tapis du salon est doux.
-narrateur|Des cubes attendent près du canapé.
-narrateur|Ils sont verts.
-narrateur|Ils sont jaunes.
-narrateur|En ce moment, Raphaël est au salon.
-narrateur|Il touche un cube jaune.
-narrateur|Le cube est lisse.
-enfant-m|Il est chaud, maman.
-maman|C'est le soleil, Raphaël.
-narrateur|Raphaël pose un cube.
-narrateur|Puis un autre cube.
+          <t>narrateur|La cuillère en bois tape dans le bol.
+narrateur|Ça sent la vanille.
+narrateur|Une buée est sur la vitre de la cuisine.
+narrateur|Une goutte glisse tout doucement.
+papa|Le gâteau est bientôt prêt.
+maman|Il sent bon, papa.
+narrateur|Dans le salon, le tapis est épais.
+narrateur|Une nappe à carreaux attend sur la chaise.
+narrateur|Elle est encore pliée.
+narrateur|Le tissu est doux.
+narrateur|Et voilà Raphaël, près du tapis.
+narrateur|Des cubes verts attendent.
+narrateur|Des cubes jaunes aussi.
+enfant-m|Je fais une tour, maman.
+maman|Pendant que le gâteau refroidit ?
+enfant-m|Oui. Une tour haute.
+narrateur|Raphaël pose un cube vert.
 narrateur|Clic.
-narrateur|La tour grandit.
-narrateur|Elle est haute.
-papa|Ta tour est belle !
-enfant-m|Elle est haute, papa.
+narrateur|Puis un cube jaune.
+narrateur|Clic.
+narrateur|La tour grandit au milieu.
+papa|Elle est belle, ta tour.
+enfant-m|Le cube du haut, c'est le gâteau.
+maman|Un gâteau de cubes !
 narrateur|Raphaël pose encore un cube.
 narrateur|Clic.
-narrateur|Puis le jeu est fini.
-maman|Le jeu est fini, Raphaël.
-maman|C'est l'heure de ranger.
-maman|Ranger, c'est mettre dans la caisse.
-narrateur|Raphaël regarde la caisse.
-narrateur|La caisse est en bois.
-narrateur|Elle sent le bois.
-narrateur|Il prend un cube jaune.
-narrateur|Il le met dans la caisse.
-narrateur|Toc.
-narrateur|Il prend un cube vert.
-narrateur|Il le met dans la caisse.
-narrateur|Toc.
-maman|Bravo, Raphaël.
-maman|Tu mets les cubes dans la caisse.
-narrateur|Encore un cube.
-narrateur|Dans la caisse.
-narrateur|Papa arrive du couloir.
-papa|Tu as fini de ranger tes jouets ?
-enfant-m|Presque, papa.
-narrateur|Raphaël prend le dernier cube.
-narrateur|Il le met dans la caisse.
-narrateur|La caisse est pleine.
-narrateur|Le tapis est vide.
-narrateur|Le soleil est encore sur le plancher.
-maman|Merci, Raphaël.
-maman|Tu as fait du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+narrateur|Il touche le cube du haut.
+narrateur|Le bois est lisse.
+enfant-m|On mange le vrai, après ?
+maman|Oui. Sur la nappe.
+narrateur|Maman prend la nappe à carreaux.
+narrateur|Elle sent un peu le savon.
+narrateur|Raphaël aide à l'ouvrir.
+narrateur|La nappe se déplie sur le tapis.
+narrateur|Un coin se replie.
+narrateur|Raphaël l'aplatit avec la main.
+narrateur|Il y a une bosse au milieu.
+enfant-m|Oh. Ça fait une bosse.
+narrateur|Un cube est sous le tissu.
+narrateur|La nappe ne peut pas être plate.
+papa|Le gâteau a besoin d'une nappe plate.
+enfant-m|Je voulais le gâteau ici.
+maman|Les cubes sont encore là.
+narrateur|La tour attend près de la chaise.
+narrateur|D'autres cubes sont sur le tapis.
+narrateur|La bosse reste au milieu.
+enfant-m|Le plat va danser.
+maman|Oui. Il faut de la place.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1409,7 +1403,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Après le jeu, que fait Léa ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Après le jeu, que fait Raphaël ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1424,7 +1418,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>ranger | la caisse | dans la caisse | elle range</t>
+          <t>ranger | la caisse | dans la caisse | il range | cubes dans la caisse</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1439,7 +1433,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle met les cubes dans la caisse. Que fait Léa ?</t>
+          <t>Il met les cubes dans la caisse. Que fait Raphaël ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1563,7 +1557,6 @@
           <t>narrateur|Après le jeu, que fait Raphaël ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1588,12 +1581,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a rangé. Les cubes sont dans la caisse. Le tapis est libre. Les pieds peuvent marcher. Le salon est calme, maintenant. Bravo. Les cubes sont rentrés dans la caisse. J'ai rangé. Oui. Ranger, c'est mettre dans la caisse. Raphaël pose la main sur le couvercle. Le bois est lisse. Tu as fini de ranger tes jouets ? Oui, papa. C'est du bon travail.</t>
+          <t>Raphaël soulève le coin de la nappe. Le cube jaune est là. Il le prend. La caisse en bois est près du canapé. Elle sent le bois. Raphaël met le cube dans la caisse. Toc. On va ranger. Les cubes vont dans la caisse. Dans la caisse. Il prend un cube vert. Il le met dans la caisse. Toc. Il prend le cube du haut de la tour. Dans la caisse aussi. La nappe redevient plate. Raphaël passe la main sur le tissu. Plus de bosse. Elle est plate, maman. Oui. Le gâteau peut venir.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa a rangé. Les cubes sont dans la &lt;emphasis level="moderate"&gt;caisse&lt;/emphasis&gt;. Le tapis est libre. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Raphaël soulève le coin de la nappe. Le cube jaune est là. Il le prend. La caisse en bois est près du canapé. Elle sent le bois. Raphaël met le cube dans la caisse. Toc. On va ranger. Les cubes vont dans la caisse. Dans la caisse. Il prend un cube vert. Il le met dans la caisse. Toc. Il prend le cube du haut de la tour. Dans la caisse aussi. La nappe redevient plate. Raphaël passe la main sur le tissu. Plus de bosse. Elle est plate, maman. Oui. Le gâteau peut venir.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1732,24 +1725,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël a rangé.
-narrateur|Les cubes sont dans la caisse.
-narrateur|Le tapis est libre.
-narrateur|Les pieds peuvent marcher.
-maman|Le salon est calme, maintenant.
-papa|Bravo.
-papa|Les cubes sont rentrés dans la caisse.
-enfant-m|J'ai rangé.
-maman|Oui.
-maman|Ranger, c'est mettre dans la caisse.
-narrateur|Raphaël pose la main sur le couvercle.
-narrateur|Le bois est lisse.
-papa|Tu as fini de ranger tes jouets ?
-enfant-m|Oui, papa.
-maman|C'est du bon travail.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël soulève le coin de la nappe.
+narrateur|Le cube jaune est là.
+narrateur|Il le prend.
+narrateur|La caisse en bois est près du canapé.
+narrateur|Elle sent le bois.
+narrateur|Raphaël met le cube dans la caisse.
+narrateur|Toc.
+papa|On va ranger.
+papa|Les cubes vont dans la caisse.
+enfant-m|Dans la caisse.
+narrateur|Il prend un cube vert.
+narrateur|Il le met dans la caisse.
+narrateur|Toc.
+narrateur|Il prend le cube du haut de la tour.
+narrateur|Dans la caisse aussi.
+maman|La nappe redevient plate.
+narrateur|Raphaël passe la main sur le tissu.
+narrateur|Plus de bosse.
+enfant-m|Elle est plate, maman.
+maman|Oui. Le gâteau peut venir.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1774,12 +1771,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Raphaël ferme la caisse. Ça fait toc. Le soleil touche le couvercle. Tu veux un peu d'eau ? Oui, maman. Maman lui tend un verre. L'eau fait un petit bruit. Raphaël boit une gorgée. Merci, Raphaël. Le salon est beau. Ils restent un moment. Le tapis est doux sous les pieds. On reste encore un peu ensemble ? Oui. Bravo.</t>
+          <t>Maman pose le petit gâteau. Il est encore un peu chaud. Ça sent la vanille. On s'assoit autour. Raphaël s'assoit sur le tapis. La nappe est plate sous le plat. Il prend un morceau. Il est doux. Oui. Tout doux. Une miette tombe. Raphaël la pose sur le plat. La tour dort, maintenant. Dans la caisse. Ils mangent un peu. La buée glisse encore sur la vitre. C'est bon, hein ? Oui. C'est bon.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Léa ferme la &lt;emphasis level="moderate"&gt;caisse&lt;/emphasis&gt;. Ça fait toc. Maman lui tend l'eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Maman pose le petit gâteau. Il est encore un peu chaud. Ça sent la vanille. On s'assoit autour. Raphaël s'assoit sur le tapis. La nappe est plate sous le plat. Il prend un morceau. Il est doux. Oui. Tout doux. Une miette tombe. Raphaël la pose sur le plat. La tour dort, maintenant. Dans la caisse. Ils mangent un peu. La buée glisse encore sur la vitre. C'est bon, hein ? Oui. C'est bon.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1914,24 +1911,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël ferme la caisse.
-narrateur|Ça fait toc.
-narrateur|Le soleil touche le couvercle.
-maman|Tu veux un peu d'eau ?
-enfant-m|Oui, maman.
-narrateur|Maman lui tend un verre.
-narrateur|L'eau fait un petit bruit.
-narrateur|Raphaël boit une gorgée.
-papa|Merci, Raphaël.
-papa|Le salon est beau.
-narrateur|Ils restent un moment.
-narrateur|Le tapis est doux sous les pieds.
-maman|On reste encore un peu ensemble ?
-enfant-m|Oui.
-maman|Bravo.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Maman pose le petit gâteau.
+narrateur|Il est encore un peu chaud.
+narrateur|Ça sent la vanille.
+papa|On s'assoit autour.
+narrateur|Raphaël s'assoit sur le tapis.
+narrateur|La nappe est plate sous le plat.
+narrateur|Il prend un morceau.
+enfant-m|Il est doux.
+maman|Oui. Tout doux.
+narrateur|Une miette tombe.
+narrateur|Raphaël la pose sur le plat.
+papa|La tour dort, maintenant.
+enfant-m|Dans la caisse.
+narrateur|Ils mangent un peu.
+narrateur|La buée glisse encore sur la vitre.
+maman|C'est bon, hein ?
+enfant-m|Oui. C'est bon.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1956,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai mis les cubes dans la caisse. Bravo. Tu as fait du bon travail. La tour est rangée. Le soleil glisse un peu. L'histoire est finie.</t>
+          <t>On a mangé le gâteau. Sur la nappe plate. Les cubes sont dans la caisse. Le salon sent encore la vanille. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>On a mangé le gâteau. Sur la nappe plate. Les cubes sont dans la caisse. Le salon sent encore la vanille. L'histoire est finie.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2096,15 +2094,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai mis les cubes dans la caisse.
-maman|Bravo.
-maman|Tu as fait du bon travail.
-papa|La tour est rangée.
-narrateur|Le soleil glisse un peu.
+          <t>enfant-m|On a mangé le gâteau.
+maman|Sur la nappe plate.
+narrateur|Les cubes sont dans la caisse.
+papa|Le salon sent encore la vanille.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2168,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
@@ -1954,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a mangé le gâteau. Sur la nappe plate. Les cubes sont dans la caisse. Le salon sent encore la vanille. L'histoire est finie.</t>
+          <t>On a mangé le gâteau. Sur la nappe plate. Les cubes sont dans la caisse. Le salon sent encore la vanille.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a mangé le gâteau. Sur la nappe plate. Les cubes sont dans la caisse. Le salon sent encore la vanille. L'histoire est finie.</t>
+          <t>On a mangé le gâteau. Sur la nappe plate. Les cubes sont dans la caisse. Le salon sent encore la vanille.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2097,8 +2097,7 @@
           <t>enfant-m|On a mangé le gâteau.
 maman|Sur la nappe plate.
 narrateur|Les cubes sont dans la caisse.
-papa|Le salon sent encore la vanille.
-narrateur|L'histoire est finie.</t>
+papa|Le salon sent encore la vanille.</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2169,6 +2168,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>salon</t>
+          <t>cuisine puis salon, après-midi du gâteau</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Léa, maman</t>
+          <t>Raphaël, papa, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine puis salon, après-midi du gâteau</t>
+          <t>cuisine à la vanille, salon, nappe à carreaux, après-midi du gâteau</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Raphaël veut le gâteau sur la nappe à carreaux. Un cube fait une bosse. Il met les cubes dans la caisse. Ils goûtent.</t>
+          <t>Raphaël veut le gâteau sur la nappe à carreaux, avec son doudou. La tour recouvre le doudou. Il met les cubes dans la caisse pour voir dessous. Le doudou apparaît. Ils goûtent.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La cuillère en bois tape dans le bol. Ça sent la vanille. Une buée est sur la vitre de la cuisine. Une goutte glisse tout doucement. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend sur la chaise. Elle est encore pliée. Le tissu est doux. Et voilà Raphaël, près du tapis. Des cubes verts attendent. Des cubes jaunes aussi. Je fais une tour, maman. Pendant que le gâteau refroidit ? Oui. Une tour haute. Raphaël pose un cube vert. Clic. Puis un cube jaune. Clic. La tour grandit au milieu. Elle est belle, ta tour. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Raphaël pose encore un cube. Clic. Il touche le cube du haut. Le bois est lisse. On mange le vrai, après ? Oui. Sur la nappe. Maman prend la nappe à carreaux. Elle sent un peu le savon. Raphaël aide à l'ouvrir. La nappe se déplie sur le tapis. Un coin se replie. Raphaël l'aplatit avec la main. Il y a une bosse au milieu. Oh. Ça fait une bosse. Un cube est sous le tissu. La nappe ne peut pas être plate. Le gâteau a besoin d'une nappe plate. Je voulais le gâteau ici. Les cubes sont encore là. La tour attend près de la chaise. D'autres cubes sont sur le tapis. La bosse reste au milieu. Le plat va danser. Oui. Il faut de la place.</t>
+          <t>La cuillère en bois tape dans le bol. Ça sent la vanille, tout chaud. Une buée perle sur la vitre. Une goutte glisse, tout doucement. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend. Elle est encore pliée, sur la chaise. Le tissu sent un peu le savon. En ce moment, Raphaël est là. Des cubes verts attendent. Des cubes jaunes aussi. Je fais une tour, maman. Pendant que le gâteau refroidit ? Oui, une tour haute. Raphaël pose un cube vert. Clic. Puis un cube jaune. Clic. La tour grandit au milieu. Elle est belle, ta tour. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Le doudou gris est au pied. Raphaël l'assoit contre la tour. Toi, tu goûtes avec nous. Il pose encore un cube. Clic. Un cube jaune glisse. La tour penche un peu. Trois cubes tombent sur le doudou. Oh. Ça a bougé. Raphaël cherche du regard. Où est mon doudou ? Sur la chaise, peut-être ? Il va vers la chaise. La nappe est là, seule. Pas de tissu gris. Sous la nappe ? Il soulève un coin doux. Rien. Près du canapé ? Sa main passe sous le coussin. Le coussin est moelleux. Le doudou n'est pas là. Il est perdu. La tour est encore au milieu. Le tapis disparaît sous les cubes. Je veux voir dessous. Raphaël prend le cube du haut. Il le pose dans la caisse. Toc. Le bois sent un peu la forêt.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La cuillère en bois tape dans le bol. Ça sent la vanille. Une buée est sur la vitre de la cuisine. Une goutte glisse tout doucement. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend sur la chaise. Elle est encore pliée. Le tissu est doux. Et voilà Raphaël, près du tapis. Des cubes verts attendent. Des cubes jaunes aussi. Je fais une tour, maman. Pendant que le gâteau refroidit ? Oui. Une tour haute. Raphaël pose un cube vert. Clic. Puis un cube jaune. Clic. La tour grandit au milieu. Elle est belle, ta tour. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Raphaël pose encore un cube. Clic. Il touche le cube du haut. Le bois est lisse. On mange le vrai, après ? Oui. Sur la nappe. Maman prend la nappe à carreaux. Elle sent un peu le savon. Raphaël aide à l'ouvrir. La nappe se déplie sur le tapis. Un coin se replie. Raphaël l'aplatit avec la main. Il y a une bosse au milieu. Oh. Ça fait une bosse. Un cube est sous le tissu. La nappe ne peut pas être plate. Le gâteau a besoin d'une nappe plate. Je voulais le gâteau ici. Les cubes sont encore là. La tour attend près de la chaise. D'autres cubes sont sur le tapis. La bosse reste au milieu. Le plat va danser. Oui. Il faut de la place.</t>
+          <t>La cuillère en bois tape dans le bol. Ça sent la vanille, tout chaud. Une buée perle sur la vitre. Une goutte glisse, tout doucement. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend. Elle est encore pliée, sur la chaise. Le tissu sent un peu le savon. En ce moment, Raphaël est là. Des cubes verts attendent. Des cubes jaunes aussi. Je fais une tour, maman. Pendant que le gâteau refroidit ? Oui, une tour haute. Raphaël pose un cube vert. Clic. Puis un cube jaune. Clic. La tour grandit au milieu. Elle est belle, ta tour. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Le doudou gris est au pied. Raphaël l'assoit contre la tour. Toi, tu goûtes avec nous. Il pose encore un cube. Clic. Un cube jaune glisse. La tour penche un peu. Trois cubes tombent sur le doudou. Oh. Ça a bougé. Raphaël cherche du regard. Où est mon doudou ? Sur la chaise, peut-être ? Il va vers la chaise. La nappe est là, seule. Pas de tissu gris. Sous la nappe ? Il soulève un coin doux. Rien. Près du canapé ? Sa main passe sous le coussin. Le coussin est moelleux. Le doudou n'est pas là. Il est perdu. La tour est encore au milieu. Le tapis disparaît sous les cubes. Je veux voir dessous. Raphaël prend le cube du haut. Il le pose dans la caisse. Toc. Le bois sent un peu la forêt.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1245,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1325,21 +1325,21 @@
       <c r="AW2" t="inlineStr">
         <is>
           <t>narrateur|La cuillère en bois tape dans le bol.
-narrateur|Ça sent la vanille.
-narrateur|Une buée est sur la vitre de la cuisine.
-narrateur|Une goutte glisse tout doucement.
+narrateur|Ça sent la vanille, tout chaud.
+narrateur|Une buée perle sur la vitre.
+narrateur|Une goutte glisse, tout doucement.
 papa|Le gâteau est bientôt prêt.
 maman|Il sent bon, papa.
 narrateur|Dans le salon, le tapis est épais.
-narrateur|Une nappe à carreaux attend sur la chaise.
-narrateur|Elle est encore pliée.
-narrateur|Le tissu est doux.
-narrateur|Et voilà Raphaël, près du tapis.
+narrateur|Une nappe à carreaux attend.
+narrateur|Elle est encore pliée, sur la chaise.
+narrateur|Le tissu sent un peu le savon.
+narrateur|En ce moment, Raphaël est là.
 narrateur|Des cubes verts attendent.
 narrateur|Des cubes jaunes aussi.
 enfant-m|Je fais une tour, maman.
 maman|Pendant que le gâteau refroidit ?
-enfant-m|Oui. Une tour haute.
+enfant-m|Oui, une tour haute.
 narrateur|Raphaël pose un cube vert.
 narrateur|Clic.
 narrateur|Puis un cube jaune.
@@ -1348,30 +1348,37 @@
 papa|Elle est belle, ta tour.
 enfant-m|Le cube du haut, c'est le gâteau.
 maman|Un gâteau de cubes !
-narrateur|Raphaël pose encore un cube.
+narrateur|Le doudou gris est au pied.
+narrateur|Raphaël l'assoit contre la tour.
+enfant-m|Toi, tu goûtes avec nous.
+narrateur|Il pose encore un cube.
 narrateur|Clic.
-narrateur|Il touche le cube du haut.
-narrateur|Le bois est lisse.
-enfant-m|On mange le vrai, après ?
-maman|Oui. Sur la nappe.
-narrateur|Maman prend la nappe à carreaux.
-narrateur|Elle sent un peu le savon.
-narrateur|Raphaël aide à l'ouvrir.
-narrateur|La nappe se déplie sur le tapis.
-narrateur|Un coin se replie.
-narrateur|Raphaël l'aplatit avec la main.
-narrateur|Il y a une bosse au milieu.
-enfant-m|Oh. Ça fait une bosse.
-narrateur|Un cube est sous le tissu.
-narrateur|La nappe ne peut pas être plate.
-papa|Le gâteau a besoin d'une nappe plate.
-enfant-m|Je voulais le gâteau ici.
-maman|Les cubes sont encore là.
-narrateur|La tour attend près de la chaise.
-narrateur|D'autres cubes sont sur le tapis.
-narrateur|La bosse reste au milieu.
-enfant-m|Le plat va danser.
-maman|Oui. Il faut de la place.</t>
+narrateur|Un cube jaune glisse.
+narrateur|La tour penche un peu.
+narrateur|Trois cubes tombent sur le doudou.
+enfant-m|Oh.
+papa|Ça a bougé.
+narrateur|Raphaël cherche du regard.
+enfant-m|Où est mon doudou ?
+maman|Sur la chaise, peut-être ?
+narrateur|Il va vers la chaise.
+narrateur|La nappe est là, seule.
+narrateur|Pas de tissu gris.
+enfant-m|Sous la nappe ?
+narrateur|Il soulève un coin doux.
+narrateur|Rien.
+papa|Près du canapé ?
+narrateur|Sa main passe sous le coussin.
+narrateur|Le coussin est moelleux.
+narrateur|Le doudou n'est pas là.
+enfant-m|Il est perdu.
+maman|La tour est encore au milieu.
+narrateur|Le tapis disparaît sous les cubes.
+enfant-m|Je veux voir dessous.
+narrateur|Raphaël prend le cube du haut.
+narrateur|Il le pose dans la caisse.
+narrateur|Toc.
+narrateur|Le bois sent un peu la forêt.</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1405,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Après le jeu, que fait Raphaël ?</t>
+          <t>Raphaël cherche son doudou. Où est-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Après le jeu, que fait Raphaël ?</t>
+          <t>Raphaël cherche son doudou. Où est-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1413,12 +1420,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>le doudou</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>ranger | la caisse | dans la caisse | il range | cubes dans la caisse</t>
+          <t>le doudou | doudou | sous la tour | sous les cubes | dessous</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1433,7 +1440,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il met les cubes dans la caisse. Que fait Raphaël ?</t>
+          <t>Il cherche sous les cubes. Où est le doudou ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1482,7 +1489,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1554,7 +1561,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Après le jeu, que fait Raphaël ?</t>
+          <t>narrateur|Raphaël cherche son doudou.
+narrateur|Où est-il ?</t>
         </is>
       </c>
     </row>
@@ -1581,12 +1589,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël soulève le coin de la nappe. Le cube jaune est là. Il le prend. La caisse en bois est près du canapé. Elle sent le bois. Raphaël met le cube dans la caisse. Toc. On va ranger. Les cubes vont dans la caisse. Dans la caisse. Il prend un cube vert. Il le met dans la caisse. Toc. Il prend le cube du haut de la tour. Dans la caisse aussi. La nappe redevient plate. Raphaël passe la main sur le tissu. Plus de bosse. Elle est plate, maman. Oui. Le gâteau peut venir.</t>
+          <t>Un cube vert reste sur le tapis. Raphaël le glisse dans la caisse. Toc. Tu regardes bien dessous ? Oui, maman. La tour devient plus petite. Un bout de tapis reparaît. Encore un, tout doux. Le cube jaune va dans la caisse. Toc. Raphaël écarte un cube bas. Un coin de tissu gris. Mon doudou ! Le doudou était sous la tour. Il sent encore le lit. Raphaël le serre contre sa joue. Le tissu est chaud, tout doux. Te voilà, petit. Merci, tu l'as trouvé. Il était dessous. La caisse a presque tous les cubes. Le tapis est libre, au milieu. La nappe peut s'ouvrir, maintenant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Raphaël soulève le coin de la nappe. Le cube jaune est là. Il le prend. La caisse en bois est près du canapé. Elle sent le bois. Raphaël met le cube dans la caisse. Toc. On va ranger. Les cubes vont dans la caisse. Dans la caisse. Il prend un cube vert. Il le met dans la caisse. Toc. Il prend le cube du haut de la tour. Dans la caisse aussi. La nappe redevient plate. Raphaël passe la main sur le tissu. Plus de bosse. Elle est plate, maman. Oui. Le gâteau peut venir.</t>
+          <t>Un cube vert reste sur le tapis. Raphaël le glisse dans la caisse. Toc. Tu regardes bien dessous ? Oui, maman. La tour devient plus petite. Un bout de tapis reparaît. Encore un, tout doux. Le cube jaune va dans la caisse. Toc. Raphaël écarte un cube bas. Un coin de tissu gris. Mon doudou ! Le doudou était sous la tour. Il sent encore le lit. Raphaël le serre contre sa joue. Le tissu est chaud, tout doux. Te voilà, petit. Merci, tu l'as trouvé. Il était dessous. La caisse a presque tous les cubes. Le tapis est libre, au milieu. La nappe peut s'ouvrir, maintenant.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1642,14 +1650,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1725,26 +1733,29 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Raphaël soulève le coin de la nappe.
-narrateur|Le cube jaune est là.
-narrateur|Il le prend.
-narrateur|La caisse en bois est près du canapé.
-narrateur|Elle sent le bois.
-narrateur|Raphaël met le cube dans la caisse.
+          <t>narrateur|Un cube vert reste sur le tapis.
+narrateur|Raphaël le glisse dans la caisse.
 narrateur|Toc.
-papa|On va ranger.
-papa|Les cubes vont dans la caisse.
-enfant-m|Dans la caisse.
-narrateur|Il prend un cube vert.
-narrateur|Il le met dans la caisse.
+maman|Tu regardes bien dessous ?
+enfant-m|Oui, maman.
+narrateur|La tour devient plus petite.
+narrateur|Un bout de tapis reparaît.
+papa|Encore un, tout doux.
+narrateur|Le cube jaune va dans la caisse.
 narrateur|Toc.
-narrateur|Il prend le cube du haut de la tour.
-narrateur|Dans la caisse aussi.
-maman|La nappe redevient plate.
-narrateur|Raphaël passe la main sur le tissu.
-narrateur|Plus de bosse.
-enfant-m|Elle est plate, maman.
-maman|Oui. Le gâteau peut venir.</t>
+narrateur|Raphaël écarte un cube bas.
+narrateur|Un coin de tissu gris.
+enfant-m|Mon doudou !
+narrateur|Le doudou était sous la tour.
+narrateur|Il sent encore le lit.
+narrateur|Raphaël le serre contre sa joue.
+narrateur|Le tissu est chaud, tout doux.
+maman|Te voilà, petit.
+papa|Merci, tu l'as trouvé.
+enfant-m|Il était dessous.
+narrateur|La caisse a presque tous les cubes.
+narrateur|Le tapis est libre, au milieu.
+maman|La nappe peut s'ouvrir, maintenant.</t>
         </is>
       </c>
     </row>
@@ -1771,12 +1782,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose le petit gâteau. Il est encore un peu chaud. Ça sent la vanille. On s'assoit autour. Raphaël s'assoit sur le tapis. La nappe est plate sous le plat. Il prend un morceau. Il est doux. Oui. Tout doux. Une miette tombe. Raphaël la pose sur le plat. La tour dort, maintenant. Dans la caisse. Ils mangent un peu. La buée glisse encore sur la vitre. C'est bon, hein ? Oui. C'est bon.</t>
+          <t>Maman déplie la nappe à carreaux. Raphaël tient un coin. Les carreaux sont rouges et blancs. La nappe est plate, enfin. Le vrai gâteau peut s'asseoir. Papa pose le plat chaud. La vanille remplit le salon. Le doudou a un carreau. Oui, le carreau rouge. Raphaël casse un bout tiède. La miette fond un peu. C'est bon, papa. On est bien, ici. Tu veux un peu d'eau ? Oui, maman. L'eau fait un petit bruit. Le soleil touche un carreau. Le doudou reste contre lui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Maman pose le petit gâteau. Il est encore un peu chaud. Ça sent la vanille. On s'assoit autour. Raphaël s'assoit sur le tapis. La nappe est plate sous le plat. Il prend un morceau. Il est doux. Oui. Tout doux. Une miette tombe. Raphaël la pose sur le plat. La tour dort, maintenant. Dans la caisse. Ils mangent un peu. La buée glisse encore sur la vitre. C'est bon, hein ? Oui. C'est bon.</t>
+          <t>Maman déplie la nappe à carreaux. Raphaël tient un coin. Les carreaux sont rouges et blancs. La nappe est plate, enfin. Le vrai gâteau peut s'asseoir. Papa pose le plat chaud. La vanille remplit le salon. Le doudou a un carreau. Oui, le carreau rouge. Raphaël casse un bout tiède. La miette fond un peu. C'est bon, papa. On est bien, ici. Tu veux un peu d'eau ? Oui, maman. L'eau fait un petit bruit. Le soleil touche un carreau. Le doudou reste contre lui.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1832,14 +1843,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1911,23 +1922,24 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman pose le petit gâteau.
-narrateur|Il est encore un peu chaud.
-narrateur|Ça sent la vanille.
-papa|On s'assoit autour.
-narrateur|Raphaël s'assoit sur le tapis.
-narrateur|La nappe est plate sous le plat.
-narrateur|Il prend un morceau.
-enfant-m|Il est doux.
-maman|Oui. Tout doux.
-narrateur|Une miette tombe.
-narrateur|Raphaël la pose sur le plat.
-papa|La tour dort, maintenant.
-enfant-m|Dans la caisse.
-narrateur|Ils mangent un peu.
-narrateur|La buée glisse encore sur la vitre.
-maman|C'est bon, hein ?
-enfant-m|Oui. C'est bon.</t>
+          <t>narrateur|Maman déplie la nappe à carreaux.
+narrateur|Raphaël tient un coin.
+narrateur|Les carreaux sont rouges et blancs.
+narrateur|La nappe est plate, enfin.
+papa|Le vrai gâteau peut s'asseoir.
+narrateur|Papa pose le plat chaud.
+narrateur|La vanille remplit le salon.
+enfant-m|Le doudou a un carreau.
+maman|Oui, le carreau rouge.
+narrateur|Raphaël casse un bout tiède.
+narrateur|La miette fond un peu.
+enfant-m|C'est bon, papa.
+papa|On est bien, ici.
+maman|Tu veux un peu d'eau ?
+enfant-m|Oui, maman.
+narrateur|L'eau fait un petit bruit.
+narrateur|Le soleil touche un carreau.
+narrateur|Le doudou reste contre lui.</t>
         </is>
       </c>
     </row>
@@ -1954,12 +1966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>On a mangé le gâteau. Sur la nappe plate. Les cubes sont dans la caisse. Le salon sent encore la vanille.</t>
+          <t>Le doudou a du gâteau. Un tout petit bout. Bravo, tu l'as retrouvé. La vanille reste dans l'air. Les carreaux sont chauds, maintenant.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>On a mangé le gâteau. Sur la nappe plate. Les cubes sont dans la caisse. Le salon sent encore la vanille.</t>
+          <t>Le doudou a du gâteau. Un tout petit bout. Bravo, tu l'as retrouvé. La vanille reste dans l'air. Les carreaux sont chauds, maintenant.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2015,14 +2027,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2094,10 +2106,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|On a mangé le gâteau.
-maman|Sur la nappe plate.
-narrateur|Les cubes sont dans la caisse.
-papa|Le salon sent encore la vanille.</t>
+          <t>enfant-m|Le doudou a du gâteau.
+maman|Un tout petit bout.
+papa|Bravo, tu l'as retrouvé.
+narrateur|La vanille reste dans l'air.
+narrateur|Les carreaux sont chauds, maintenant.</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2131,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2175,6 +2188,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Raphaël veut le gâteau sur la nappe à carreaux, avec son doudou. La tour recouvre le doudou. Il met les cubes dans la caisse pour voir dessous. Le doudou apparaît. Ils goûtent.</t>
+          <t>La vanille arrive dans le salon, avant le gâteau. Sur un carreau rouge, un éclat de nappe brille. Raphaël veut la tour haute, maintenant, avec le doudou. Un cube glisse : le doudou disparaît. Il cherche sous la nappe, sous le coussin, puis prend toute la pile : les cubes s'éparpillent. Il refuse de foncer, pose un cube, retrouve le doudou. Sur la nappe ouverte, l'éclat de nappe tient au carreau du doudou.</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La cuillère en bois tape dans le bol. Ça sent la vanille, tout chaud. Une buée perle sur la vitre. Une goutte glisse, tout doucement. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend. Elle est encore pliée, sur la chaise. Le tissu sent un peu le savon. En ce moment, Raphaël est là. Des cubes verts attendent. Des cubes jaunes aussi. Je fais une tour, maman. Pendant que le gâteau refroidit ? Oui, une tour haute. Raphaël pose un cube vert. Clic. Puis un cube jaune. Clic. La tour grandit au milieu. Elle est belle, ta tour. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Le doudou gris est au pied. Raphaël l'assoit contre la tour. Toi, tu goûtes avec nous. Il pose encore un cube. Clic. Un cube jaune glisse. La tour penche un peu. Trois cubes tombent sur le doudou. Oh. Ça a bougé. Raphaël cherche du regard. Où est mon doudou ? Sur la chaise, peut-être ? Il va vers la chaise. La nappe est là, seule. Pas de tissu gris. Sous la nappe ? Il soulève un coin doux. Rien. Près du canapé ? Sa main passe sous le coussin. Le coussin est moelleux. Le doudou n'est pas là. Il est perdu. La tour est encore au milieu. Le tapis disparaît sous les cubes. Je veux voir dessous. Raphaël prend le cube du haut. Il le pose dans la caisse. Toc. Le bois sent un peu la forêt.</t>
+          <t>La vanille arrive dans le salon, avant le gâteau. Un carré de buée s'ouvre sur la vitre. La cuillère en bois tape dans le bol. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend, pliée. Elle repose sur la chaise. Sur un carreau rouge, un éclat de nappe brille. Il est tout petit, maman. C'est un éclat de nappe. Le tissu sent un peu le savon. Raphaël, tu sens le gâteau ? Oui, papa. Je veux la tour, maintenant ! Pendant que le gâteau refroidit ? Oui, une tour haute. En ce moment, Raphaël saisit un cube. Le cube vert est lisse, un peu froid. Il le pose au milieu du tapis. Ça fait clic, tout petit. Puis un cube jaune. Ça fait clic, contre le vert. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Le doudou gris est au pied. Raphaël l'assoit contre la tour. Toi, tu goûtes avec nous. Elle est belle, ta tour. Raphaël veut un cube de plus. Il le pose trop vite. Un cube jaune glisse. La tour penche. Trois cubes tombent sur le doudou. Oh. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Où est mon doudou ? Sous la nappe, peut-être ? Il va vers la chaise. Il soulève un coin du tissu. L'éclat de nappe tremble, puis tient. Pas de tissu gris. Il n'est pas là. Près du canapé ? Sa main passe sous le coussin. Le coussin est moelleux. Le doudou n'est pas là. Il est perdu. Je prends tout, d'un coup ! Il saisit la pile trop vite. Les cubes glissent entre ses doigts. Le tapis disparaît sous les cubes. Ça ne veut pas, papa. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu regardes sous les cubes ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La cuillère en bois tape dans le bol. Ça sent la vanille, tout chaud. Une buée perle sur la vitre. Une goutte glisse, tout doucement. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend. Elle est encore pliée, sur la chaise. Le tissu sent un peu le savon. En ce moment, Raphaël est là. Des cubes verts attendent. Des cubes jaunes aussi. Je fais une tour, maman. Pendant que le gâteau refroidit ? Oui, une tour haute. Raphaël pose un cube vert. Clic. Puis un cube jaune. Clic. La tour grandit au milieu. Elle est belle, ta tour. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Le doudou gris est au pied. Raphaël l'assoit contre la tour. Toi, tu goûtes avec nous. Il pose encore un cube. Clic. Un cube jaune glisse. La tour penche un peu. Trois cubes tombent sur le doudou. Oh. Ça a bougé. Raphaël cherche du regard. Où est mon doudou ? Sur la chaise, peut-être ? Il va vers la chaise. La nappe est là, seule. Pas de tissu gris. Sous la nappe ? Il soulève un coin doux. Rien. Près du canapé ? Sa main passe sous le coussin. Le coussin est moelleux. Le doudou n'est pas là. Il est perdu. La tour est encore au milieu. Le tapis disparaît sous les cubes. Je veux voir dessous. Raphaël prend le cube du haut. Il le pose dans la caisse. Toc. Le bois sent un peu la forêt.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La vanille arrive dans le salon, avant le gâteau. Un carré de buée s'ouvre sur la vitre. La cuillère en bois tape dans le bol. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend, pliée. Elle repose sur la chaise. Sur un carreau rouge, un &lt;emphasis level="moderate"&gt;éclat de nappe&lt;/emphasis&gt; brille. Il est tout petit, maman. C'est un éclat de nappe. Le tissu sent un peu le savon. Raphaël, tu sens le gâteau ? Oui, papa. Je veux la tour, maintenant ! Pendant que le gâteau refroidit ? Oui, une tour haute. En ce moment, Raphaël saisit un cube. Le cube vert est lisse, un peu froid. Il le pose au milieu du tapis. Ça fait clic, tout petit. Puis un cube jaune. Ça fait clic, contre le vert. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Le doudou gris est au pied. Raphaël l'assoit contre la tour. Toi, tu goûtes avec nous. Elle est belle, ta tour. Raphaël veut un cube de plus. Il le pose trop vite. Un cube jaune glisse. La tour penche. Trois cubes tombent sur le doudou. Oh. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Où est mon doudou ? Sous la nappe, peut-être ? Il va vers la chaise. Il soulève un coin du tissu. L'éclat de nappe tremble, puis tient. Pas de tissu gris. Il n'est pas là. Près du canapé ? Sa main passe sous le coussin. Le coussin est moelleux. Le doudou n'est pas là. Il est perdu. Je prends tout, d'un coup ! Il saisit la pile trop vite. Les cubes glissent entre ses doigts. Le tapis disparaît sous les cubes. Ça ne veut pas, papa. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu regardes sous les cubes ?&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Léa joue dans le salon. Maman est sur le canapé. Léa a des cubes. Les cubes sont verts et jaunes. Léa fait une tour. La tour est haute. Les cubes font clic. Puis le jeu est fini. Maman dit : c'est l'heure de &lt;emphasis&gt;ranger&lt;/emphasis&gt;. Léa prend un cube. Elle le met dans la caisse. Elle prend un autre cube. Elle le met dans la caisse. Encore un cube. Dans la caisse. La caisse est pleine. Le tapis est vide. Ranger, c'est mettre dans la caisse. Maman dit : merci Léa.&lt;/slow&gt; [pause]</t>
+          <t>La vanille arrive dans le salon, avant le gâteau. Un carré de buée s'ouvre sur la vitre. La cuillère en bois tape dans le bol. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend, pliée. Elle repose sur la chaise. Sur un carreau rouge, un &lt;emphasis&gt;éclat de nappe&lt;/emphasis&gt; brille. Il est tout petit, maman. C'est un éclat de nappe. Le tissu sent un peu le savon. Raphaël, tu sens le gâteau ? Oui, papa. Je veux la tour, maintenant ! Pendant que le gâteau refroidit ? Oui, une tour haute. En ce moment, Raphaël saisit un cube. Le cube vert est lisse, un peu froid. Il le pose au milieu du tapis. Ça fait clic, tout petit. Puis un cube jaune. Ça fait clic, contre le vert. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Le doudou gris est au pied. Raphaël l'assoit contre la tour. Toi, tu goûtes avec nous. Elle est belle, ta tour. Raphaël veut un cube de plus. Il le pose trop vite. Un cube jaune glisse. La tour penche. Trois cubes tombent sur le doudou. Oh. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Où est mon doudou ? Sous la nappe, peut-être ? Il va vers la chaise. Il soulève un coin du tissu. L'éclat de nappe tremble, puis tient. Pas de tissu gris. Il n'est pas là. Près du canapé ? Sa main passe sous le coussin. Le coussin est moelleux. Le doudou n'est pas là. Il est perdu. Je prends tout, d'un coup ! Il saisit la pile trop vite. Les cubes glissent entre ses doigts. Le tapis disparaît sous les cubes. Ça ne veut pas, papa. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu regardes sous les cubes ? [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1241,7 +1241,7 @@
         </is>
       </c>
       <c r="Y2" s="2" t="n">
-        <v>118</v>
+        <v>142</v>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1275,30 +1275,30 @@
       </c>
       <c r="AH2" s="2" t="inlineStr">
         <is>
-          <t>ranger</t>
+          <t>éclat de nappe</t>
         </is>
       </c>
       <c r="AI2" s="2" t="n">
         <v>0</v>
       </c>
       <c r="AJ2" s="2" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AK2" s="2" t="n">
-        <v>380</v>
+        <v>260</v>
       </c>
       <c r="AL2" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>warm</t>
         </is>
       </c>
       <c r="AM2" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>storytelling</t>
         </is>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>0.333</v>
+        <v>0.36</v>
       </c>
       <c r="AO2" s="2" t="inlineStr"/>
       <c r="AP2" s="2" t="inlineStr">
@@ -1307,10 +1307,10 @@
         </is>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AR2" s="2" t="n">
-        <v>0.86</v>
+        <v>0.98</v>
       </c>
       <c r="AS2" s="2" t="n">
         <v>100</v>
@@ -1319,66 +1319,77 @@
         <v>50</v>
       </c>
       <c r="AU2" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV2" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>arc=installation; intention=émerveiller puis tendre; emotion=impatience puis découragement; intensite=2; destinataire=enfant; sous_texte=il_veut_la_tour_maintenant; tempo=naturel puis resserré; sourire=léger puis aucun; respiration=ample puis retenue</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La cuillère en bois tape dans le bol.
-narrateur|Ça sent la vanille, tout chaud.
-narrateur|Une buée perle sur la vitre.
-narrateur|Une goutte glisse, tout doucement.
+          <t>narrateur|La vanille arrive dans le salon, avant le gâteau.
+narrateur|Un carré de buée s'ouvre sur la vitre.
+narrateur|La cuillère en bois tape dans le bol.
 papa|Le gâteau est bientôt prêt.
 maman|Il sent bon, papa.
 narrateur|Dans le salon, le tapis est épais.
-narrateur|Une nappe à carreaux attend.
-narrateur|Elle est encore pliée, sur la chaise.
+narrateur|Une nappe à carreaux attend, pliée.
+narrateur|Elle repose sur la chaise.
+narrateur|Sur un carreau rouge, un éclat de nappe brille.
+enfant-m|Il est tout petit, maman.
+maman|C'est un éclat de nappe.
 narrateur|Le tissu sent un peu le savon.
-narrateur|En ce moment, Raphaël est là.
-narrateur|Des cubes verts attendent.
-narrateur|Des cubes jaunes aussi.
-enfant-m|Je fais une tour, maman.
+papa|Raphaël, tu sens le gâteau ?
+enfant-m|Oui, papa.
+enfant-m|Je veux la tour, maintenant !
 maman|Pendant que le gâteau refroidit ?
 enfant-m|Oui, une tour haute.
-narrateur|Raphaël pose un cube vert.
-narrateur|Clic.
+narrateur|En ce moment, Raphaël saisit un cube.
+narrateur|Le cube vert est lisse, un peu froid.
+narrateur|Il le pose au milieu du tapis.
+narrateur|Ça fait clic, tout petit.
 narrateur|Puis un cube jaune.
-narrateur|Clic.
-narrateur|La tour grandit au milieu.
-papa|Elle est belle, ta tour.
+narrateur|Ça fait clic, contre le vert.
 enfant-m|Le cube du haut, c'est le gâteau.
 maman|Un gâteau de cubes !
 narrateur|Le doudou gris est au pied.
 narrateur|Raphaël l'assoit contre la tour.
 enfant-m|Toi, tu goûtes avec nous.
-narrateur|Il pose encore un cube.
-narrateur|Clic.
+papa|Elle est belle, ta tour.
+narrateur|Raphaël veut un cube de plus.
+narrateur|Il le pose trop vite.
 narrateur|Un cube jaune glisse.
-narrateur|La tour penche un peu.
+narrateur|La tour penche.
 narrateur|Trois cubes tombent sur le doudou.
 enfant-m|Oh.
-papa|Ça a bougé.
-narrateur|Raphaël cherche du regard.
+narrateur|Le sourire de Raphaël disparaît.
+narrateur|Dans sa poitrine, l'envie et l'inquiétude se bousculent.
 enfant-m|Où est mon doudou ?
-maman|Sur la chaise, peut-être ?
+maman|Sous la nappe, peut-être ?
 narrateur|Il va vers la chaise.
-narrateur|La nappe est là, seule.
+narrateur|Il soulève un coin du tissu.
+narrateur|L'éclat de nappe tremble, puis tient.
 narrateur|Pas de tissu gris.
-enfant-m|Sous la nappe ?
-narrateur|Il soulève un coin doux.
-narrateur|Rien.
+enfant-m|Il n'est pas là.
 papa|Près du canapé ?
 narrateur|Sa main passe sous le coussin.
 narrateur|Le coussin est moelleux.
 narrateur|Le doudou n'est pas là.
 enfant-m|Il est perdu.
-maman|La tour est encore au milieu.
+enfant-m|Je prends tout, d'un coup !
+narrateur|Il saisit la pile trop vite.
+narrateur|Les cubes glissent entre ses doigts.
 narrateur|Le tapis disparaît sous les cubes.
-enfant-m|Je veux voir dessous.
-narrateur|Raphaël prend le cube du haut.
-narrateur|Il le pose dans la caisse.
-narrateur|Toc.
-narrateur|Le bois sent un peu la forêt.</t>
+enfant-m|Ça ne veut pas, papa.
+narrateur|Ses épaules tombent un peu.
+narrateur|Papa se baisse à sa hauteur.
+papa|Tu regardes sous les cubes ?</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>cuillère,cubes</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1421,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Raphaël cherche son doudou. Où est-il ?</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Raphaël cherche son &lt;emphasis level="moderate"&gt;doudou&lt;/emphasis&gt;. Où est-il ?&lt;/prosody&gt;&lt;break time="700ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Après le jeu, que fait Léa ?&lt;/slow&gt;</t>
+          <t>&lt;soft&gt;&lt;slow&gt;Raphaël cherche son &lt;emphasis&gt;doudou&lt;/emphasis&gt;. Où est-il ?&lt;/slow&gt;&lt;/soft&gt; [pause]</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -1478,7 +1489,7 @@
         </is>
       </c>
       <c r="Y3" s="2" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
@@ -1486,10 +1497,10 @@
         </is>
       </c>
       <c r="AA3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1504,34 +1515,38 @@
       <c r="AE3" s="2" t="inlineStr"/>
       <c r="AF3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>soft</t>
         </is>
       </c>
       <c r="AG3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH3" s="2" t="inlineStr"/>
+        <v>-2</v>
+      </c>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>doudou</t>
+        </is>
+      </c>
       <c r="AI3" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ3" s="2" t="n">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AK3" s="2" t="n">
-        <v>380</v>
+        <v>320</v>
       </c>
       <c r="AL3" s="2" t="inlineStr">
         <is>
-          <t>warm</t>
+          <t>focused</t>
         </is>
       </c>
       <c r="AM3" s="2" t="inlineStr">
         <is>
-          <t>rise</t>
+          <t>rising</t>
         </is>
       </c>
       <c r="AN3" s="2" t="n">
-        <v>0.333</v>
+        <v>0.32</v>
       </c>
       <c r="AO3" s="2" t="inlineStr"/>
       <c r="AP3" s="2" t="inlineStr">
@@ -1540,13 +1555,13 @@
         </is>
       </c>
       <c r="AQ3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AR3" s="2" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="AS3" s="2" t="n">
-        <v>100</v>
+        <v>82</v>
       </c>
       <c r="AT3" s="2" t="n">
         <v>50</v>
@@ -1556,7 +1571,7 @@
       </c>
       <c r="AV3" s="2" t="inlineStr">
         <is>
-          <t>question d'écoute, ne change pas le cours</t>
+          <t>arc=indice; intention=faire_deviner; emotion=attention; intensite=1; destinataire=enfant; sous_texte=le_doudou_est_sous_les_cubes; tempo=suspendu; sourire=aucun; respiration=courte_avant_question</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
@@ -1589,17 +1604,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Un cube vert reste sur le tapis. Raphaël le glisse dans la caisse. Toc. Tu regardes bien dessous ? Oui, maman. La tour devient plus petite. Un bout de tapis reparaît. Encore un, tout doux. Le cube jaune va dans la caisse. Toc. Raphaël écarte un cube bas. Un coin de tissu gris. Mon doudou ! Le doudou était sous la tour. Il sent encore le lit. Raphaël le serre contre sa joue. Le tissu est chaud, tout doux. Te voilà, petit. Merci, tu l'as trouvé. Il était dessous. La caisse a presque tous les cubes. Le tapis est libre, au milieu. La nappe peut s'ouvrir, maintenant.</t>
+          <t>Raphaël refuse de prendre toute la pile. Il pose un genou au tapis. Un cube vert reste près de sa main. Je le mets tout seul. Il glisse le cube dans la caisse. Toc. Le bois sent un peu la forêt. Tu regardes bien dessous ? Oui, maman. La tour devient plus petite. Un bout de tapis reparaît. Le cube jaune va dans la caisse. Toc. Je sors le reste, d'un coup ! Il tire trop fort sur un cube bas. Deux cubes retombent, comme un toit. Oh. Il ne reprend pas trop vite. Il écoute le salon, un instant. Sur la chaise, l'éclat de nappe brille. Il est là. Raphaël refuse de foncer. Il écarte un cube, lentement. Un coin de tissu gris. Mon doudou ! Le doudou était sous la tour. Il sent le tapis, un peu chaud. Raphaël le serre contre sa joue. Merci, Raphaël. Il était dessous. La caisse a presque tous les cubes. Le tapis est libre, au milieu. La nappe peut s'ouvrir ? Oui, maman. Raphaël pose la main sur le doudou. Le tissu est un peu rêche.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Un cube vert reste sur le tapis. Raphaël le glisse dans la caisse. Toc. Tu regardes bien dessous ? Oui, maman. La tour devient plus petite. Un bout de tapis reparaît. Encore un, tout doux. Le cube jaune va dans la caisse. Toc. Raphaël écarte un cube bas. Un coin de tissu gris. Mon doudou ! Le doudou était sous la tour. Il sent encore le lit. Raphaël le serre contre sa joue. Le tissu est chaud, tout doux. Te voilà, petit. Merci, tu l'as trouvé. Il était dessous. La caisse a presque tous les cubes. Le tapis est libre, au milieu. La nappe peut s'ouvrir, maintenant.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Raphaël refuse de prendre toute la pile. Il pose un genou au tapis. Un cube vert reste près de sa main. Je le mets tout seul. Il glisse le cube dans la &lt;emphasis level="moderate"&gt;caisse&lt;/emphasis&gt;. Toc. Le bois sent un peu la forêt. Tu regardes bien dessous ? Oui, maman. La tour devient plus petite. Un bout de tapis reparaît. Le cube jaune va dans la caisse. Toc. Je sors le reste, d'un coup ! Il tire trop fort sur un cube bas. Deux cubes retombent, comme un toit. Oh. Il ne reprend pas trop vite. Il écoute le salon, un instant. Sur la chaise, l'éclat de nappe brille. Il est là. Raphaël refuse de foncer. Il écarte un cube, lentement. Un coin de tissu gris. Mon doudou ! Le doudou était sous la tour. Il sent le tapis, un peu chaud. Raphaël le serre contre sa joue. Merci, Raphaël. Il était dessous. La caisse a presque tous les cubes. Le tapis est libre, au milieu. La nappe peut s'ouvrir ? Oui, maman. Raphaël pose la main sur le doudou. Le tissu est un peu rêche.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Léa a rangé. Les cubes sont dans la &lt;emphasis&gt;caisse&lt;/emphasis&gt;. Le tapis est libre. Maman est là.&lt;/slow&gt; [pause]</t>
+          <t>Raphaël refuse de prendre toute la pile. Il pose un genou au tapis. Un cube vert reste près de sa main. Je le mets tout seul. Il glisse le cube dans la &lt;emphasis&gt;caisse&lt;/emphasis&gt;. Toc. Le bois sent un peu la forêt. Tu regardes bien dessous ? Oui, maman. La tour devient plus petite. Un bout de tapis reparaît. Le cube jaune va dans la caisse. Toc. Je sors le reste, d'un coup ! Il tire trop fort sur un cube bas. Deux cubes retombent, comme un toit. Oh. Il ne reprend pas trop vite. Il écoute le salon, un instant. Sur la chaise, l'éclat de nappe brille. Il est là. Raphaël refuse de foncer. Il écarte un cube, lentement. Un coin de tissu gris. Mon doudou ! Le doudou était sous la tour. Il sent le tapis, un peu chaud. Raphaël le serre contre sa joue. Merci, Raphaël. Il était dessous. La caisse a presque tous les cubes. Le tapis est libre, au milieu. La nappe peut s'ouvrir ? Oui, maman. Raphaël pose la main sur le doudou. Le tissu est un peu rêche. [pause]</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr"/>
@@ -1646,7 +1661,7 @@
         </is>
       </c>
       <c r="Y4" s="2" t="n">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
@@ -1654,10 +1669,10 @@
         </is>
       </c>
       <c r="AA4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.22</v>
+        <v>1.14</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1687,23 +1702,23 @@
         <v>200</v>
       </c>
       <c r="AJ4" s="2" t="n">
-        <v>450</v>
+        <v>560</v>
       </c>
       <c r="AK4" s="2" t="n">
-        <v>380</v>
+        <v>270</v>
       </c>
       <c r="AL4" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>bright</t>
         </is>
       </c>
       <c r="AM4" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN4" s="2" t="n">
-        <v>0.333</v>
+        <v>0.35</v>
       </c>
       <c r="AO4" s="2" t="inlineStr"/>
       <c r="AP4" s="2" t="inlineStr">
@@ -1712,10 +1727,10 @@
         </is>
       </c>
       <c r="AQ4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AR4" s="2" t="n">
-        <v>0.86</v>
+        <v>0.97</v>
       </c>
       <c r="AS4" s="2" t="n">
         <v>100</v>
@@ -1724,38 +1739,56 @@
         <v>50</v>
       </c>
       <c r="AU4" s="2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr">
         <is>
-          <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
+          <t>arc=résolution; intention=faire_vivre_le_geste; emotion=concentration puis fierté_calme; intensite=2; destinataire=enfant; sous_texte=il_pose_un_cube_sans_foncer; tempo=naturel; sourire=léger; respiration=relâchée</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Un cube vert reste sur le tapis.
-narrateur|Raphaël le glisse dans la caisse.
+          <t>narrateur|Raphaël refuse de prendre toute la pile.
+narrateur|Il pose un genou au tapis.
+narrateur|Un cube vert reste près de sa main.
+enfant-m|Je le mets tout seul.
+narrateur|Il glisse le cube dans la caisse.
 narrateur|Toc.
+narrateur|Le bois sent un peu la forêt.
 maman|Tu regardes bien dessous ?
 enfant-m|Oui, maman.
 narrateur|La tour devient plus petite.
 narrateur|Un bout de tapis reparaît.
-papa|Encore un, tout doux.
 narrateur|Le cube jaune va dans la caisse.
 narrateur|Toc.
-narrateur|Raphaël écarte un cube bas.
+enfant-m|Je sors le reste, d'un coup !
+narrateur|Il tire trop fort sur un cube bas.
+narrateur|Deux cubes retombent, comme un toit.
+enfant-m|Oh.
+narrateur|Il ne reprend pas trop vite.
+narrateur|Il écoute le salon, un instant.
+narrateur|Sur la chaise, l'éclat de nappe brille.
+enfant-m|Il est là.
+narrateur|Raphaël refuse de foncer.
+narrateur|Il écarte un cube, lentement.
 narrateur|Un coin de tissu gris.
 enfant-m|Mon doudou !
 narrateur|Le doudou était sous la tour.
-narrateur|Il sent encore le lit.
+narrateur|Il sent le tapis, un peu chaud.
 narrateur|Raphaël le serre contre sa joue.
-narrateur|Le tissu est chaud, tout doux.
-maman|Te voilà, petit.
-papa|Merci, tu l'as trouvé.
+papa|Merci, Raphaël.
 enfant-m|Il était dessous.
 narrateur|La caisse a presque tous les cubes.
 narrateur|Le tapis est libre, au milieu.
-maman|La nappe peut s'ouvrir, maintenant.</t>
+maman|La nappe peut s'ouvrir ?
+enfant-m|Oui, maman.
+narrateur|Raphaël pose la main sur le doudou.
+narrateur|Le tissu est un peu rêche.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>caisse,bois</t>
         </is>
       </c>
     </row>
@@ -1782,17 +1815,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Maman déplie la nappe à carreaux. Raphaël tient un coin. Les carreaux sont rouges et blancs. La nappe est plate, enfin. Le vrai gâteau peut s'asseoir. Papa pose le plat chaud. La vanille remplit le salon. Le doudou a un carreau. Oui, le carreau rouge. Raphaël casse un bout tiède. La miette fond un peu. C'est bon, papa. On est bien, ici. Tu veux un peu d'eau ? Oui, maman. L'eau fait un petit bruit. Le soleil touche un carreau. Le doudou reste contre lui.</t>
+          <t>On déplie la nappe ? Maman déplie la nappe à carreaux. Raphaël tient un coin. Les carreaux sont rouges et blancs. Un cube oublié accroche le tissu. Je tire ! Raphaël s'arrête. Il refuse de foncer. Il recule le cube, lentement. La nappe se pose, plate. Le vrai gâteau peut s'asseoir. Papa pose le plat chaud. La vanille remplit le salon. Le doudou a un carreau. Oui, le carreau rouge. L'éclat de nappe tremble sur le rouge. Tu veux un peu d'eau ? Oui, papa. L'eau fait un petit bruit. Raphaël casse un bout tiède. La miette fond un peu. C'est bon, papa. On est bien, ici. Le doudou reste contre lui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Maman déplie la nappe à carreaux. Raphaël tient un coin. Les carreaux sont rouges et blancs. La nappe est plate, enfin. Le vrai gâteau peut s'asseoir. Papa pose le plat chaud. La vanille remplit le salon. Le doudou a un carreau. Oui, le carreau rouge. Raphaël casse un bout tiède. La miette fond un peu. C'est bon, papa. On est bien, ici. Tu veux un peu d'eau ? Oui, maman. L'eau fait un petit bruit. Le soleil touche un carreau. Le doudou reste contre lui.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On déplie la &lt;emphasis level="moderate"&gt;nappe&lt;/emphasis&gt; ? Maman déplie la nappe à carreaux. Raphaël tient un coin. Les carreaux sont rouges et blancs. Un cube oublié accroche le tissu. Je tire ! Raphaël s'arrête. Il refuse de foncer. Il recule le cube, lentement. La nappe se pose, plate. Le vrai gâteau peut s'asseoir. Papa pose le plat chaud. La vanille remplit le salon. Le doudou a un carreau. Oui, le carreau rouge. L'éclat de nappe tremble sur le rouge. Tu veux un peu d'eau ? Oui, papa. L'eau fait un petit bruit. Raphaël casse un bout tiède. La miette fond un peu. C'est bon, papa. On est bien, ici. Le doudou reste contre lui.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>&lt;slow&gt;Léa ferme la &lt;emphasis&gt;caisse&lt;/emphasis&gt;. Ça fait toc. Maman lui tend l'eau.&lt;/slow&gt; [pause]</t>
+          <t>On déplie la &lt;emphasis&gt;nappe&lt;/emphasis&gt; ? Maman déplie la nappe à carreaux. Raphaël tient un coin. Les carreaux sont rouges et blancs. Un cube oublié accroche le tissu. Je tire ! Raphaël s'arrête. Il refuse de foncer. Il recule le cube, lentement. La nappe se pose, plate. Le vrai gâteau peut s'asseoir. Papa pose le plat chaud. La vanille remplit le salon. Le doudou a un carreau. Oui, le carreau rouge. L'éclat de nappe tremble sur le rouge. Tu veux un peu d'eau ? Oui, papa. L'eau fait un petit bruit. Raphaël casse un bout tiède. La miette fond un peu. C'est bon, papa. On est bien, ici. Le doudou reste contre lui. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1839,7 +1872,7 @@
         </is>
       </c>
       <c r="Y5" s="2" t="n">
-        <v>118</v>
+        <v>146</v>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
@@ -1847,10 +1880,10 @@
         </is>
       </c>
       <c r="AA5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1873,30 +1906,30 @@
       </c>
       <c r="AH5" s="2" t="inlineStr">
         <is>
-          <t>caisse</t>
+          <t>nappe</t>
         </is>
       </c>
       <c r="AI5" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ5" s="2" t="n">
-        <v>450</v>
+        <v>420</v>
       </c>
       <c r="AK5" s="2" t="n">
-        <v>380</v>
+        <v>250</v>
       </c>
       <c r="AL5" s="2" t="inlineStr">
         <is>
-          <t>calm</t>
+          <t>lively</t>
         </is>
       </c>
       <c r="AM5" s="2" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>dynamic</t>
         </is>
       </c>
       <c r="AN5" s="2" t="n">
-        <v>0.333</v>
+        <v>0.37</v>
       </c>
       <c r="AO5" s="2" t="inlineStr"/>
       <c r="AP5" s="2" t="inlineStr">
@@ -1905,10 +1938,10 @@
         </is>
       </c>
       <c r="AQ5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR5" s="2" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AS5" s="2" t="n">
         <v>100</v>
@@ -1917,29 +1950,44 @@
         <v>50</v>
       </c>
       <c r="AU5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV5" s="2" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>arc=action; intention=entraîner; emotion=élan puis prudence; intensite=2; destinataire=enfant; sous_texte=il_refuse_de_tirer_la_nappe; tempo=vif puis posé; sourire=léger; respiration=courte</t>
+        </is>
+      </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Maman déplie la nappe à carreaux.
+          <t>papa|On déplie la nappe ?
+narrateur|Maman déplie la nappe à carreaux.
 narrateur|Raphaël tient un coin.
 narrateur|Les carreaux sont rouges et blancs.
-narrateur|La nappe est plate, enfin.
+narrateur|Un cube oublié accroche le tissu.
+enfant-m|Je tire !
+narrateur|Raphaël s'arrête.
+narrateur|Il refuse de foncer.
+narrateur|Il recule le cube, lentement.
+narrateur|La nappe se pose, plate.
 papa|Le vrai gâteau peut s'asseoir.
 narrateur|Papa pose le plat chaud.
 narrateur|La vanille remplit le salon.
 enfant-m|Le doudou a un carreau.
 maman|Oui, le carreau rouge.
+narrateur|L'éclat de nappe tremble sur le rouge.
+papa|Tu veux un peu d'eau ?
+enfant-m|Oui, papa.
+narrateur|L'eau fait un petit bruit.
 narrateur|Raphaël casse un bout tiède.
 narrateur|La miette fond un peu.
 enfant-m|C'est bon, papa.
-papa|On est bien, ici.
-maman|Tu veux un peu d'eau ?
-enfant-m|Oui, maman.
-narrateur|L'eau fait un petit bruit.
-narrateur|Le soleil touche un carreau.
+maman|On est bien, ici.
 narrateur|Le doudou reste contre lui.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>nappe,plat</t>
         </is>
       </c>
     </row>
@@ -1966,17 +2014,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Le doudou a du gâteau. Un tout petit bout. Bravo, tu l'as retrouvé. La vanille reste dans l'air. Les carreaux sont chauds, maintenant.</t>
+          <t>Ils s'assoient près de la nappe tiède. La chaleur touche les joues de Raphaël. Le gâteau est là. Oui, tout chaud. Le doudou a un tout petit bout. Comme l'éclat de nappe, papa ! Tu le vois, toi ? Oui, sur le carreau rouge. Raphaël glisse le doudou sans se presser. Le tissu repose contre sa hanche. On le sent, maman. Tu le sens sur tes joues ? Oui, il est chaud. La vanille reste dans l'air. L'éclat de nappe tient sur le carreau.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Le doudou a du gâteau. Un tout petit bout. Bravo, tu l'as retrouvé. La vanille reste dans l'air. Les carreaux sont chauds, maintenant.</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils s'assoient près de la nappe tiède. La chaleur touche les joues de Raphaël. Le gâteau est là. Oui, tout chaud. Le doudou a un tout petit bout. Comme l'&lt;emphasis level="moderate"&gt;éclat de nappe&lt;/emphasis&gt;, papa ! Tu le vois, toi ? Oui, sur le carreau rouge. Raphaël glisse le doudou sans se presser. Le tissu repose contre sa hanche. On le sent, maman. Tu le sens sur tes joues ? Oui, il est chaud. La vanille reste dans l'air. L'éclat de nappe tient sur le carreau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;lower-pitch&gt;&lt;soft&gt;&lt;slow&gt;L'histoire est finie.&lt;/slow&gt;&lt;/soft&gt;&lt;/lower-pitch&gt; [pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils s'assoient près de la nappe tiède. La chaleur touche les joues de Raphaël. Le gâteau est là. Oui, tout chaud. Le doudou a un tout petit bout. Comme l'&lt;emphasis&gt;éclat de nappe&lt;/emphasis&gt;, papa ! Tu le vois, toi ? Oui, sur le carreau rouge. Raphaël glisse le doudou sans se presser. Le tissu repose contre sa hanche. On le sent, maman. Tu le sens sur tes joues ? Oui, il est chaud. La vanille reste dans l'air. L'éclat de nappe tient sur le carreau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2023,18 +2071,18 @@
         </is>
       </c>
       <c r="Y6" s="2" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2043,12 +2091,12 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>-2st</t>
         </is>
       </c>
       <c r="AE6" s="2" t="inlineStr">
         <is>
-          <t>lower-pitch</t>
+          <t>low-pitch</t>
         </is>
       </c>
       <c r="AF6" s="2" t="inlineStr">
@@ -2057,17 +2105,21 @@
         </is>
       </c>
       <c r="AG6" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="AH6" s="2" t="inlineStr"/>
+        <v>-3</v>
+      </c>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>éclat de nappe</t>
+        </is>
+      </c>
       <c r="AI6" s="2" t="n">
         <v>200</v>
       </c>
       <c r="AJ6" s="2" t="n">
-        <v>600</v>
+        <v>900</v>
       </c>
       <c r="AK6" s="2" t="n">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AL6" s="2" t="inlineStr">
         <is>
@@ -2076,11 +2128,11 @@
       </c>
       <c r="AM6" s="2" t="inlineStr">
         <is>
-          <t>fall</t>
+          <t>falling</t>
         </is>
       </c>
       <c r="AN6" s="2" t="n">
-        <v>0.333</v>
+        <v>0.31</v>
       </c>
       <c r="AO6" s="2" t="inlineStr"/>
       <c r="AP6" s="2" t="inlineStr">
@@ -2089,28 +2141,47 @@
         </is>
       </c>
       <c r="AQ6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AR6" s="2" t="n">
-        <v>0.82</v>
+        <v>0.85</v>
       </c>
       <c r="AS6" s="2" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="AT6" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="AU6" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>arc=retour; intention=refermer; emotion=tendresse et fierté_calme; intensite=1; destinataire=enfant; sous_texte=l_eclat_du_debut_tient_sur_le_carreau; tempo=posé; sourire=léger; respiration=ample</t>
+        </is>
+      </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|Le doudou a du gâteau.
-maman|Un tout petit bout.
-papa|Bravo, tu l'as retrouvé.
+          <t>narrateur|Ils s'assoient près de la nappe tiède.
+narrateur|La chaleur touche les joues de Raphaël.
+enfant-m|Le gâteau est là.
+maman|Oui, tout chaud.
+narrateur|Le doudou a un tout petit bout.
+enfant-m|Comme l'éclat de nappe, papa !
+papa|Tu le vois, toi ?
+enfant-m|Oui, sur le carreau rouge.
+narrateur|Raphaël glisse le doudou sans se presser.
+narrateur|Le tissu repose contre sa hanche.
+enfant-m|On le sent, maman.
+maman|Tu le sens sur tes joues ?
+enfant-m|Oui, il est chaud.
 narrateur|La vanille reste dans l'air.
-narrateur|Les carreaux sont chauds, maintenant.</t>
+narrateur|L'éclat de nappe tient sur le carreau.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>gâteau,vanille</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A9"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2195,6 +2266,13 @@
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>

--- a/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
+++ b/stories/arbres/ATOM-AUT.RAN.001-01.xlsx
@@ -1184,17 +1184,17 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vanille arrive dans le salon, avant le gâteau. Un carré de buée s'ouvre sur la vitre. La cuillère en bois tape dans le bol. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend, pliée. Elle repose sur la chaise. Sur un carreau rouge, un éclat de nappe brille. Il est tout petit, maman. C'est un éclat de nappe. Le tissu sent un peu le savon. Raphaël, tu sens le gâteau ? Oui, papa. Je veux la tour, maintenant ! Pendant que le gâteau refroidit ? Oui, une tour haute. En ce moment, Raphaël saisit un cube. Le cube vert est lisse, un peu froid. Il le pose au milieu du tapis. Ça fait clic, tout petit. Puis un cube jaune. Ça fait clic, contre le vert. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Le doudou gris est au pied. Raphaël l'assoit contre la tour. Toi, tu goûtes avec nous. Elle est belle, ta tour. Raphaël veut un cube de plus. Il le pose trop vite. Un cube jaune glisse. La tour penche. Trois cubes tombent sur le doudou. Oh. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Où est mon doudou ? Sous la nappe, peut-être ? Il va vers la chaise. Il soulève un coin du tissu. L'éclat de nappe tremble, puis tient. Pas de tissu gris. Il n'est pas là. Près du canapé ? Sa main passe sous le coussin. Le coussin est moelleux. Le doudou n'est pas là. Il est perdu. Je prends tout, d'un coup ! Il saisit la pile trop vite. Les cubes glissent entre ses doigts. Le tapis disparaît sous les cubes. Ça ne veut pas, papa. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu regardes sous les cubes ?</t>
+          <t>La vanille arrive dans le salon, avant le gâteau. Un carré de buée s'ouvre sur la vitre. La cuillère en bois tape dans le bol. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend, pliée. Elle repose sur la chaise. Sur un carreau rouge, un éclat de nappe brille. Il est tout petit, maman. C'est le soleil sur le rouge. Le tissu sent un peu le savon. Raphaël, tu sens le gâteau ? Oui, papa. Je veux la tour, maintenant ! Pendant que le gâteau refroidit ? Oui, une tour haute. En ce moment, Raphaël saisit un cube. Le cube vert est lisse, un peu froid. Il le pose au milieu du tapis. Ça fait clic, tout petit. Puis un cube jaune. Ça fait clic, contre le vert. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Le doudou gris est au pied. Raphaël l'assoit contre la tour. Toi, tu goûtes avec nous. Elle est belle, ta tour. Raphaël veut un cube de plus. Il le pose trop vite. Un cube jaune glisse. La tour penche. Trois cubes tombent sur le doudou. Oh. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Où est mon doudou ? Sous la nappe, peut-être ? Il va vers la chaise. Il soulève un coin du tissu. L'éclat de nappe tremble, puis tient. Pas de tissu gris. Il n'est pas là. Près du canapé ? Sa main passe sous le coussin. Le coussin est moelleux. Le doudou n'est pas là. Il est perdu. Je prends tout, d'un coup ! Il saisit la pile trop vite. Les cubes glissent entre ses doigts. Le tapis disparaît sous les cubes. Ça ne veut pas, papa. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu regardes sous les cubes ?</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La vanille arrive dans le salon, avant le gâteau. Un carré de buée s'ouvre sur la vitre. La cuillère en bois tape dans le bol. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend, pliée. Elle repose sur la chaise. Sur un carreau rouge, un &lt;emphasis level="moderate"&gt;éclat de nappe&lt;/emphasis&gt; brille. Il est tout petit, maman. C'est un éclat de nappe. Le tissu sent un peu le savon. Raphaël, tu sens le gâteau ? Oui, papa. Je veux la tour, maintenant ! Pendant que le gâteau refroidit ? Oui, une tour haute. En ce moment, Raphaël saisit un cube. Le cube vert est lisse, un peu froid. Il le pose au milieu du tapis. Ça fait clic, tout petit. Puis un cube jaune. Ça fait clic, contre le vert. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Le doudou gris est au pied. Raphaël l'assoit contre la tour. Toi, tu goûtes avec nous. Elle est belle, ta tour. Raphaël veut un cube de plus. Il le pose trop vite. Un cube jaune glisse. La tour penche. Trois cubes tombent sur le doudou. Oh. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Où est mon doudou ? Sous la nappe, peut-être ? Il va vers la chaise. Il soulève un coin du tissu. L'éclat de nappe tremble, puis tient. Pas de tissu gris. Il n'est pas là. Près du canapé ? Sa main passe sous le coussin. Le coussin est moelleux. Le doudou n'est pas là. Il est perdu. Je prends tout, d'un coup ! Il saisit la pile trop vite. Les cubes glissent entre ses doigts. Le tapis disparaît sous les cubes. Ça ne veut pas, papa. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu regardes sous les cubes ?&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;La vanille arrive dans le salon, avant le gâteau. Un carré de buée s'ouvre sur la vitre. La cuillère en bois tape dans le bol. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend, pliée. Elle repose sur la chaise. Sur un carreau rouge, un &lt;emphasis level="moderate"&gt;éclat de nappe&lt;/emphasis&gt; brille. Il est tout petit, maman. C'est le soleil sur le rouge. Le tissu sent un peu le savon. Raphaël, tu sens le gâteau ? Oui, papa. Je veux la tour, maintenant ! Pendant que le gâteau refroidit ? Oui, une tour haute. En ce moment, Raphaël saisit un cube. Le cube vert est lisse, un peu froid. Il le pose au milieu du tapis. Ça fait clic, tout petit. Puis un cube jaune. Ça fait clic, contre le vert. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Le doudou gris est au pied. Raphaël l'assoit contre la tour. Toi, tu goûtes avec nous. Elle est belle, ta tour. Raphaël veut un cube de plus. Il le pose trop vite. Un cube jaune glisse. La tour penche. Trois cubes tombent sur le doudou. Oh. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Où est mon doudou ? Sous la nappe, peut-être ? Il va vers la chaise. Il soulève un coin du tissu. L'éclat de nappe tremble, puis tient. Pas de tissu gris. Il n'est pas là. Près du canapé ? Sa main passe sous le coussin. Le coussin est moelleux. Le doudou n'est pas là. Il est perdu. Je prends tout, d'un coup ! Il saisit la pile trop vite. Les cubes glissent entre ses doigts. Le tapis disparaît sous les cubes. Ça ne veut pas, papa. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu regardes sous les cubes ?&lt;/prosody&gt;&lt;break time="500ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>La vanille arrive dans le salon, avant le gâteau. Un carré de buée s'ouvre sur la vitre. La cuillère en bois tape dans le bol. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend, pliée. Elle repose sur la chaise. Sur un carreau rouge, un &lt;emphasis&gt;éclat de nappe&lt;/emphasis&gt; brille. Il est tout petit, maman. C'est un éclat de nappe. Le tissu sent un peu le savon. Raphaël, tu sens le gâteau ? Oui, papa. Je veux la tour, maintenant ! Pendant que le gâteau refroidit ? Oui, une tour haute. En ce moment, Raphaël saisit un cube. Le cube vert est lisse, un peu froid. Il le pose au milieu du tapis. Ça fait clic, tout petit. Puis un cube jaune. Ça fait clic, contre le vert. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Le doudou gris est au pied. Raphaël l'assoit contre la tour. Toi, tu goûtes avec nous. Elle est belle, ta tour. Raphaël veut un cube de plus. Il le pose trop vite. Un cube jaune glisse. La tour penche. Trois cubes tombent sur le doudou. Oh. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Où est mon doudou ? Sous la nappe, peut-être ? Il va vers la chaise. Il soulève un coin du tissu. L'éclat de nappe tremble, puis tient. Pas de tissu gris. Il n'est pas là. Près du canapé ? Sa main passe sous le coussin. Le coussin est moelleux. Le doudou n'est pas là. Il est perdu. Je prends tout, d'un coup ! Il saisit la pile trop vite. Les cubes glissent entre ses doigts. Le tapis disparaît sous les cubes. Ça ne veut pas, papa. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu regardes sous les cubes ? [pause]</t>
+          <t>La vanille arrive dans le salon, avant le gâteau. Un carré de buée s'ouvre sur la vitre. La cuillère en bois tape dans le bol. Le gâteau est bientôt prêt. Il sent bon, papa. Dans le salon, le tapis est épais. Une nappe à carreaux attend, pliée. Elle repose sur la chaise. Sur un carreau rouge, un &lt;emphasis&gt;éclat de nappe&lt;/emphasis&gt; brille. Il est tout petit, maman. C'est le soleil sur le rouge. Le tissu sent un peu le savon. Raphaël, tu sens le gâteau ? Oui, papa. Je veux la tour, maintenant ! Pendant que le gâteau refroidit ? Oui, une tour haute. En ce moment, Raphaël saisit un cube. Le cube vert est lisse, un peu froid. Il le pose au milieu du tapis. Ça fait clic, tout petit. Puis un cube jaune. Ça fait clic, contre le vert. Le cube du haut, c'est le gâteau. Un gâteau de cubes ! Le doudou gris est au pied. Raphaël l'assoit contre la tour. Toi, tu goûtes avec nous. Elle est belle, ta tour. Raphaël veut un cube de plus. Il le pose trop vite. Un cube jaune glisse. La tour penche. Trois cubes tombent sur le doudou. Oh. Le sourire de Raphaël disparaît. Dans sa poitrine, l'envie et l'inquiétude se bousculent. Où est mon doudou ? Sous la nappe, peut-être ? Il va vers la chaise. Il soulève un coin du tissu. L'éclat de nappe tremble, puis tient. Pas de tissu gris. Il n'est pas là. Près du canapé ? Sa main passe sous le coussin. Le coussin est moelleux. Le doudou n'est pas là. Il est perdu. Je prends tout, d'un coup ! Il saisit la pile trop vite. Les cubes glissent entre ses doigts. Le tapis disparaît sous les cubes. Ça ne veut pas, papa. Ses épaules tombent un peu. Papa se baisse à sa hauteur. Tu regardes sous les cubes ? [pause]</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr"/>
@@ -1338,7 +1338,7 @@
 narrateur|Elle repose sur la chaise.
 narrateur|Sur un carreau rouge, un éclat de nappe brille.
 enfant-m|Il est tout petit, maman.
-maman|C'est un éclat de nappe.
+maman|C'est le soleil sur le rouge.
 narrateur|Le tissu sent un peu le savon.
 papa|Raphaël, tu sens le gâteau ?
 enfant-m|Oui, papa.
@@ -1815,17 +1815,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>On déplie la nappe ? Maman déplie la nappe à carreaux. Raphaël tient un coin. Les carreaux sont rouges et blancs. Un cube oublié accroche le tissu. Je tire ! Raphaël s'arrête. Il refuse de foncer. Il recule le cube, lentement. La nappe se pose, plate. Le vrai gâteau peut s'asseoir. Papa pose le plat chaud. La vanille remplit le salon. Le doudou a un carreau. Oui, le carreau rouge. L'éclat de nappe tremble sur le rouge. Tu veux un peu d'eau ? Oui, papa. L'eau fait un petit bruit. Raphaël casse un bout tiède. La miette fond un peu. C'est bon, papa. On est bien, ici. Le doudou reste contre lui.</t>
+          <t>On déplie la nappe ? Maman déplie la nappe à carreaux. Raphaël tient un coin. Les carreaux sont rouges et blancs. Un cube oublié accroche le tissu. Je tire ! Raphaël s'arrête. Il refuse de foncer. Il recule le cube, lentement. La nappe se pose, plate. Le vrai gâteau peut s'asseoir. Papa pose le plat chaud. La vanille remplit le salon. Le doudou a un carreau. Oui, le carreau rouge. Le carreau rouge tremble un peu. Tu veux un peu d'eau ? Oui, papa. L'eau fait un petit bruit. Raphaël casse un bout tiède. La miette fond un peu. C'est bon, papa. On est bien, ici. Le doudou reste contre lui.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On déplie la &lt;emphasis level="moderate"&gt;nappe&lt;/emphasis&gt; ? Maman déplie la nappe à carreaux. Raphaël tient un coin. Les carreaux sont rouges et blancs. Un cube oublié accroche le tissu. Je tire ! Raphaël s'arrête. Il refuse de foncer. Il recule le cube, lentement. La nappe se pose, plate. Le vrai gâteau peut s'asseoir. Papa pose le plat chaud. La vanille remplit le salon. Le doudou a un carreau. Oui, le carreau rouge. L'éclat de nappe tremble sur le rouge. Tu veux un peu d'eau ? Oui, papa. L'eau fait un petit bruit. Raphaël casse un bout tiède. La miette fond un peu. C'est bon, papa. On est bien, ici. Le doudou reste contre lui.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;On déplie la &lt;emphasis level="moderate"&gt;nappe&lt;/emphasis&gt; ? Maman déplie la nappe à carreaux. Raphaël tient un coin. Les carreaux sont rouges et blancs. Un cube oublié accroche le tissu. Je tire ! Raphaël s'arrête. Il refuse de foncer. Il recule le cube, lentement. La nappe se pose, plate. Le vrai gâteau peut s'asseoir. Papa pose le plat chaud. La vanille remplit le salon. Le doudou a un carreau. Oui, le carreau rouge. Le carreau rouge tremble un peu. Tu veux un peu d'eau ? Oui, papa. L'eau fait un petit bruit. Raphaël casse un bout tiède. La miette fond un peu. C'est bon, papa. On est bien, ici. Le doudou reste contre lui.&lt;/prosody&gt;&lt;break time="420ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>On déplie la &lt;emphasis&gt;nappe&lt;/emphasis&gt; ? Maman déplie la nappe à carreaux. Raphaël tient un coin. Les carreaux sont rouges et blancs. Un cube oublié accroche le tissu. Je tire ! Raphaël s'arrête. Il refuse de foncer. Il recule le cube, lentement. La nappe se pose, plate. Le vrai gâteau peut s'asseoir. Papa pose le plat chaud. La vanille remplit le salon. Le doudou a un carreau. Oui, le carreau rouge. L'éclat de nappe tremble sur le rouge. Tu veux un peu d'eau ? Oui, papa. L'eau fait un petit bruit. Raphaël casse un bout tiède. La miette fond un peu. C'est bon, papa. On est bien, ici. Le doudou reste contre lui. [pause]</t>
+          <t>On déplie la &lt;emphasis&gt;nappe&lt;/emphasis&gt; ? Maman déplie la nappe à carreaux. Raphaël tient un coin. Les carreaux sont rouges et blancs. Un cube oublié accroche le tissu. Je tire ! Raphaël s'arrête. Il refuse de foncer. Il recule le cube, lentement. La nappe se pose, plate. Le vrai gâteau peut s'asseoir. Papa pose le plat chaud. La vanille remplit le salon. Le doudou a un carreau. Oui, le carreau rouge. Le carreau rouge tremble un peu. Tu veux un peu d'eau ? Oui, papa. L'eau fait un petit bruit. Raphaël casse un bout tiède. La miette fond un peu. C'est bon, papa. On est bien, ici. Le doudou reste contre lui. [pause]</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr"/>
@@ -1974,7 +1974,7 @@
 narrateur|La vanille remplit le salon.
 enfant-m|Le doudou a un carreau.
 maman|Oui, le carreau rouge.
-narrateur|L'éclat de nappe tremble sur le rouge.
+narrateur|Le carreau rouge tremble un peu.
 papa|Tu veux un peu d'eau ?
 enfant-m|Oui, papa.
 narrateur|L'eau fait un petit bruit.
@@ -2014,17 +2014,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Ils s'assoient près de la nappe tiède. La chaleur touche les joues de Raphaël. Le gâteau est là. Oui, tout chaud. Le doudou a un tout petit bout. Comme l'éclat de nappe, papa ! Tu le vois, toi ? Oui, sur le carreau rouge. Raphaël glisse le doudou sans se presser. Le tissu repose contre sa hanche. On le sent, maman. Tu le sens sur tes joues ? Oui, il est chaud. La vanille reste dans l'air. L'éclat de nappe tient sur le carreau.</t>
+          <t>Ils s'assoient près de la nappe tiède. La chaleur touche les joues de Raphaël. Le gâteau est là. Oui, tout chaud. Le doudou a un tout petit bout. Comme sur la chaise, papa ! Tu le vois, toi ? Oui, sur le carreau rouge. Raphaël glisse le doudou sans se presser. Le tissu repose contre sa hanche. On le sent, maman. Tu le sens sur tes joues ? Oui, il est chaud. La vanille reste dans l'air. L'éclat de nappe tient sur le carreau.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils s'assoient près de la nappe tiède. La chaleur touche les joues de Raphaël. Le gâteau est là. Oui, tout chaud. Le doudou a un tout petit bout. Comme l'&lt;emphasis level="moderate"&gt;éclat de nappe&lt;/emphasis&gt;, papa ! Tu le vois, toi ? Oui, sur le carreau rouge. Raphaël glisse le doudou sans se presser. Le tissu repose contre sa hanche. On le sent, maman. Tu le sens sur tes joues ? Oui, il est chaud. La vanille reste dans l'air. L'éclat de nappe tient sur le carreau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="-2st"&gt;Ils s'assoient près de la nappe tiède. La chaleur touche les joues de Raphaël. Le gâteau est là. Oui, tout chaud. Le doudou a un tout petit bout. Comme sur la chaise, papa ! Tu le vois, toi ? Oui, sur le carreau rouge. Raphaël glisse le doudou sans se presser. Le tissu repose contre sa hanche. On le sent, maman. Tu le sens sur tes joues ? Oui, il est chaud. La vanille reste dans l'air. L'&lt;emphasis level="moderate"&gt;éclat de nappe&lt;/emphasis&gt; tient sur le carreau.&lt;/prosody&gt;&lt;break time="900ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils s'assoient près de la nappe tiède. La chaleur touche les joues de Raphaël. Le gâteau est là. Oui, tout chaud. Le doudou a un tout petit bout. Comme l'&lt;emphasis&gt;éclat de nappe&lt;/emphasis&gt;, papa ! Tu le vois, toi ? Oui, sur le carreau rouge. Raphaël glisse le doudou sans se presser. Le tissu repose contre sa hanche. On le sent, maman. Tu le sens sur tes joues ? Oui, il est chaud. La vanille reste dans l'air. L'éclat de nappe tient sur le carreau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
+          <t>&lt;low-pitch&gt;&lt;soft&gt;&lt;slow&gt;Ils s'assoient près de la nappe tiède. La chaleur touche les joues de Raphaël. Le gâteau est là. Oui, tout chaud. Le doudou a un tout petit bout. Comme sur la chaise, papa ! Tu le vois, toi ? Oui, sur le carreau rouge. Raphaël glisse le doudou sans se presser. Le tissu repose contre sa hanche. On le sent, maman. Tu le sens sur tes joues ? Oui, il est chaud. La vanille reste dans l'air. L'&lt;emphasis&gt;éclat de nappe&lt;/emphasis&gt; tient sur le carreau.&lt;/slow&gt;&lt;/soft&gt;&lt;/low-pitch&gt; [long-pause]</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr"/>
@@ -2167,7 +2167,7 @@
 enfant-m|Le gâteau est là.
 maman|Oui, tout chaud.
 narrateur|Le doudou a un tout petit bout.
-enfant-m|Comme l'éclat de nappe, papa !
+enfant-m|Comme sur la chaise, papa !
 papa|Tu le vois, toi ?
 enfant-m|Oui, sur le carreau rouge.
 narrateur|Raphaël glisse le doudou sans se presser.
@@ -2202,7 +2202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2273,6 +2273,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
